--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -44,8 +44,8 @@
     <definedName name="Templates">#REF!</definedName>
     <definedName name="hronSEC">#REF!</definedName>
     <definedName localSheetId="0" name="SMETA_TITLE">EXPORT_TMP!$B$7</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_F449C9FB_110E_4907_A94A_54D72BF9B0FC_.wvu.FilterData">EXPORT_TMP!$I$1:$I$563</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_3A8DA5CB_6C4D_47B2_A680_E0971AEA3492_.wvu.FilterData">EXPORT_TMP!$I$1:$I$563</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_B11FEEE2_625F_4AAF_8B49_E70FE5F66624_.wvu.FilterData">EXPORT_TMP!$I$1:$I$563</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_E030274F_D8A4_4B1C_84F1_2CAF425A2CE5_.wvu.FilterData">EXPORT_TMP!$I$1:$I$563</definedName>
     <definedName name="CLIENT_PRICE">LAMBDA(себестоимость, вашмаркап, налог, округление, IFERROR(ROUNDUP(себестоимость*(1+вашмаркап/100)/(1-1*налог),округление),0))</definedName>
     <definedName name="CONDUCT_CALC">LAMBDA(стоимость, количество, налог, IFERROR(PRODUCT(количество, стоимость) / TAX_CONVERTER(налог), 0))</definedName>
     <definedName name="MARKET_FEE">LAMBDA(процент, сумма_до_налога, MIN(сумма_до_налога, 2000000) * процент + MAX(0, сумма_до_налога - 2000000) * (процент / 2))</definedName>
@@ -53,8 +53,8 @@
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{F449C9FB-110E-4907-A94A-54D72BF9B0FC}" name="nozero"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{3A8DA5CB-6C4D-47B2-A680-E0971AEA3492}" name="WithZeros"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{B11FEEE2-625F-4AAF-8B49-E70FE5F66624}" name="nozero"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{E030274F-D8A4-4B1C-84F1-2CAF425A2CE5}" name="WithZeros"/>
   </customWorkbookViews>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -198,7 +198,7 @@
     <numFmt numFmtId="164" formatCode="\+#\ \(###\)\ ###\-##\-##"/>
     <numFmt numFmtId="165" formatCode="[$-FC19]dd\ mmmm\ yyyy\ \г\."/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -344,11 +344,6 @@
       <color theme="1"/>
       <name val="Montserrat"/>
     </font>
-    <font>
-      <sz val="12.0"/>
-      <color theme="0"/>
-      <name val="Montserrat"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -385,20 +380,6 @@
       <right/>
       <top/>
       <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
     </border>
     <border>
       <left/>
@@ -453,6 +434,20 @@
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
       <right style="thin">
         <color rgb="FFFFFFFF"/>
       </right>
@@ -614,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="78">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -630,28 +625,27 @@
     <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="6" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf borderId="3" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="10" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -682,7 +676,6 @@
     </xf>
     <xf borderId="21" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="22" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="10" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="2" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
@@ -710,15 +703,12 @@
     <xf borderId="2" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf borderId="3" fillId="3" fontId="15" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="10" fillId="3" fontId="15" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf borderId="2" fillId="2" fontId="15" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -731,10 +721,10 @@
     <xf borderId="2" fillId="2" fontId="17" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -746,7 +736,7 @@
     <xf borderId="2" fillId="2" fontId="12" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf borderId="14" fillId="3" fontId="16" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -819,7 +809,7 @@
     <xf borderId="28" fillId="3" fontId="26" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="27" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1070,1662 +1060,1391 @@
       <c r="G1" s="5"/>
       <c r="H1" s="3"/>
       <c r="I1" s="6"/>
-      <c r="J1" s="7"/>
     </row>
     <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="8"/>
-      <c r="B2" s="9" t="e">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="12" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="7"/>
+      <c r="I2" s="12"/>
     </row>
     <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="8"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="12" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="13"/>
-      <c r="J3" s="7"/>
+      <c r="I3" s="12"/>
     </row>
     <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="8"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="7"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12"/>
     </row>
     <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="8"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="20">
+      <c r="A5" s="7"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="19">
         <v>7.4951331645E10</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="22" t="s">
+      <c r="D5" s="20"/>
+      <c r="E5" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="24" t="s">
+      <c r="F5" s="22"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="13"/>
-      <c r="J5" s="7"/>
+      <c r="I5" s="12"/>
     </row>
     <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="7"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="12"/>
     </row>
     <row r="7" ht="28.5" customHeight="1">
-      <c r="A7" s="8"/>
-      <c r="B7" s="28" t="s">
+      <c r="A7" s="7"/>
+      <c r="B7" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="31"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="12"/>
     </row>
     <row r="8" ht="13.5" customHeight="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="32" t="s">
+      <c r="A8" s="7"/>
+      <c r="B8" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="7"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="12"/>
     </row>
     <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="36" t="s">
+      <c r="A9" s="7"/>
+      <c r="B9" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="35">
         <v>1.0</v>
       </c>
-      <c r="D9" s="38"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="40" t="s">
+      <c r="D9" s="36"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="39">
         <v>30.0</v>
       </c>
-      <c r="H9" s="42" t="s">
+      <c r="H9" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="13"/>
-      <c r="J9" s="43"/>
+      <c r="I9" s="12"/>
     </row>
     <row r="10" ht="13.5" customHeight="1">
-      <c r="A10" s="8"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="43"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="45"/>
     </row>
     <row r="11" ht="13.5" customHeight="1">
-      <c r="A11" s="49"/>
-      <c r="B11" s="36" t="s">
+      <c r="A11" s="46"/>
+      <c r="B11" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="35">
         <v>0.0</v>
       </c>
-      <c r="D11" s="42"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="40" t="s">
+      <c r="D11" s="40"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="39">
         <v>30.0</v>
       </c>
-      <c r="H11" s="42" t="s">
+      <c r="H11" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="43"/>
+      <c r="I11" s="12"/>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="8"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="7"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="12"/>
     </row>
     <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="36" t="s">
+      <c r="A13" s="50"/>
+      <c r="B13" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="54" t="s">
+      <c r="C13" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="7"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="12"/>
     </row>
     <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="53"/>
-      <c r="B14" s="55"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="7"/>
+      <c r="A14" s="50"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="12"/>
     </row>
     <row r="15" ht="13.5" customHeight="1">
-      <c r="A15" s="8"/>
-      <c r="B15" s="36" t="s">
+      <c r="A15" s="7"/>
+      <c r="B15" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="7"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="12"/>
     </row>
     <row r="16" ht="13.5" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="55"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="7"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="12"/>
     </row>
     <row r="17" ht="13.5" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="36" t="s">
+      <c r="A17" s="7"/>
+      <c r="B17" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="7"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="12"/>
     </row>
     <row r="18" ht="13.5" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="7"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="12"/>
     </row>
     <row r="19" ht="13.5" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" s="36" t="s">
+      <c r="A19" s="7"/>
+      <c r="B19" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="62">
+      <c r="C19" s="59">
         <v>1.0</v>
       </c>
-      <c r="D19" s="63" t="s">
+      <c r="D19" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="23"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="64">
+      <c r="E19" s="22"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="61">
         <v>10.0</v>
       </c>
-      <c r="H19" s="42" t="s">
+      <c r="H19" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="I19" s="13"/>
-      <c r="J19" s="7"/>
+      <c r="I19" s="12"/>
     </row>
     <row r="20" ht="13.5" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="66" t="s">
+      <c r="A20" s="7"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="68"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="7"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="12"/>
     </row>
     <row r="21" ht="13.5" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="36" t="s">
+      <c r="A21" s="7"/>
+      <c r="B21" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="69">
+      <c r="C21" s="66">
         <v>45809.654539027775</v>
       </c>
-      <c r="D21" s="21"/>
-      <c r="E21" s="70" t="s">
+      <c r="D21" s="20"/>
+      <c r="E21" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="7"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="12"/>
     </row>
     <row r="22" ht="13.5" customHeight="1">
-      <c r="A22" s="49"/>
-      <c r="B22" s="36" t="s">
+      <c r="A22" s="46"/>
+      <c r="B22" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="71" t="s">
+      <c r="C22" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="43"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="45"/>
     </row>
     <row r="23" ht="13.5" customHeight="1">
-      <c r="A23" s="49"/>
-      <c r="B23" s="36" t="s">
+      <c r="A23" s="46"/>
+      <c r="B23" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="71" t="s">
+      <c r="C23" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="7"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="45"/>
     </row>
     <row r="24" ht="13.5" customHeight="1">
-      <c r="A24" s="49"/>
-      <c r="B24" s="36"/>
-      <c r="C24" s="71" t="s">
+      <c r="A24" s="46"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="7"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="45"/>
     </row>
     <row r="25" ht="13.5" customHeight="1">
-      <c r="A25" s="49"/>
-      <c r="B25" s="36"/>
-      <c r="C25" s="71" t="s">
+      <c r="A25" s="46"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="7"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="45"/>
     </row>
     <row r="26" ht="13.5" customHeight="1">
-      <c r="A26" s="49"/>
-      <c r="B26" s="36" t="s">
+      <c r="A26" s="46"/>
+      <c r="B26" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="71" t="s">
+      <c r="C26" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="7"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="45"/>
     </row>
     <row r="27" ht="63.75" customHeight="1">
-      <c r="A27" s="49"/>
-      <c r="B27" s="36" t="s">
+      <c r="A27" s="46"/>
+      <c r="B27" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="72" t="s">
+      <c r="C27" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="7"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="12"/>
     </row>
     <row r="28" ht="13.5" customHeight="1">
-      <c r="A28" s="49"/>
-      <c r="B28" s="36"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="7"/>
+      <c r="A28" s="46"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="69"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="12"/>
     </row>
     <row r="29" ht="13.5" customHeight="1">
-      <c r="A29" s="8"/>
-      <c r="B29" s="73" t="s">
+      <c r="A29" s="7"/>
+      <c r="B29" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="74"/>
-      <c r="D29" s="75"/>
-      <c r="E29" s="75"/>
-      <c r="F29" s="75"/>
-      <c r="G29" s="76"/>
-      <c r="H29" s="76" t="s">
+      <c r="C29" s="71"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="72"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="I29" s="13"/>
-      <c r="J29" s="7"/>
+      <c r="I29" s="12"/>
     </row>
     <row r="30" ht="13.5" customHeight="1">
-      <c r="A30" s="49"/>
-      <c r="B30" s="77" t="s">
+      <c r="A30" s="46"/>
+      <c r="B30" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="78" t="s">
+      <c r="C30" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="77" t="s">
+      <c r="D30" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="77" t="s">
+      <c r="E30" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="77" t="s">
+      <c r="F30" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="G30" s="77" t="s">
+      <c r="G30" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="H30" s="79" t="s">
+      <c r="H30" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="I30" s="13"/>
-      <c r="J30" s="80"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="49"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
+      <c r="A31" s="46"/>
+      <c r="I31" s="77"/>
     </row>
     <row r="32" ht="13.5" customHeight="1">
-      <c r="A32" s="49"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
+      <c r="A32" s="46"/>
+      <c r="I32" s="77"/>
     </row>
     <row r="33" ht="13.5" customHeight="1">
-      <c r="A33" s="49"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
+      <c r="A33" s="46"/>
+      <c r="I33" s="77"/>
     </row>
     <row r="34" ht="13.5" customHeight="1">
-      <c r="A34" s="49"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
+      <c r="A34" s="46"/>
+      <c r="I34" s="77"/>
     </row>
     <row r="35" ht="13.5" customHeight="1">
-      <c r="A35" s="49"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
+      <c r="A35" s="46"/>
+      <c r="I35" s="77"/>
     </row>
     <row r="36" ht="13.5" customHeight="1">
-      <c r="A36" s="49"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
+      <c r="A36" s="46"/>
+      <c r="I36" s="77"/>
     </row>
     <row r="37" ht="13.5" customHeight="1">
-      <c r="A37" s="49"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
+      <c r="A37" s="46"/>
+      <c r="I37" s="77"/>
     </row>
     <row r="38" ht="13.5" customHeight="1">
-      <c r="A38" s="49"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
+      <c r="A38" s="46"/>
+      <c r="I38" s="77"/>
     </row>
     <row r="39" ht="13.5" customHeight="1">
-      <c r="A39" s="49"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
+      <c r="A39" s="46"/>
+      <c r="I39" s="77"/>
     </row>
     <row r="40" ht="13.5" customHeight="1">
-      <c r="A40" s="49"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
+      <c r="A40" s="46"/>
+      <c r="I40" s="77"/>
     </row>
     <row r="41" ht="13.5" customHeight="1">
-      <c r="A41" s="49"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
+      <c r="A41" s="46"/>
+      <c r="I41" s="77"/>
     </row>
     <row r="42" ht="13.5" customHeight="1">
-      <c r="A42" s="49"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
+      <c r="A42" s="46"/>
+      <c r="I42" s="77"/>
     </row>
     <row r="43" ht="13.5" customHeight="1">
-      <c r="A43" s="49"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
+      <c r="A43" s="46"/>
+      <c r="I43" s="77"/>
     </row>
     <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="49"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
+      <c r="A44" s="46"/>
+      <c r="I44" s="77"/>
     </row>
     <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="49"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
+      <c r="A45" s="46"/>
+      <c r="I45" s="77"/>
     </row>
     <row r="46" ht="13.5" customHeight="1">
-      <c r="A46" s="49"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
+      <c r="A46" s="46"/>
+      <c r="I46" s="77"/>
     </row>
     <row r="47" ht="13.5" customHeight="1">
-      <c r="A47" s="49"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
+      <c r="A47" s="46"/>
+      <c r="I47" s="77"/>
     </row>
     <row r="48" ht="13.5" customHeight="1">
-      <c r="A48" s="49"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
+      <c r="A48" s="46"/>
+      <c r="I48" s="77"/>
     </row>
     <row r="49" ht="13.5" customHeight="1">
-      <c r="A49" s="49"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
+      <c r="A49" s="46"/>
+      <c r="I49" s="77"/>
     </row>
     <row r="50" ht="13.5" customHeight="1">
-      <c r="A50" s="49"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
+      <c r="A50" s="46"/>
+      <c r="I50" s="77"/>
     </row>
     <row r="51" ht="13.5" customHeight="1">
-      <c r="A51" s="49"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
+      <c r="A51" s="46"/>
+      <c r="I51" s="77"/>
     </row>
     <row r="52" ht="13.5" customHeight="1">
-      <c r="A52" s="49"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
+      <c r="A52" s="46"/>
+      <c r="I52" s="77"/>
     </row>
     <row r="53" ht="13.5" customHeight="1">
-      <c r="A53" s="49"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
+      <c r="A53" s="46"/>
+      <c r="I53" s="77"/>
     </row>
     <row r="54" ht="13.5" customHeight="1">
-      <c r="A54" s="49"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
+      <c r="A54" s="46"/>
+      <c r="I54" s="77"/>
     </row>
     <row r="55" ht="13.5" customHeight="1">
-      <c r="A55" s="49"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
+      <c r="A55" s="46"/>
+      <c r="I55" s="77"/>
     </row>
     <row r="56" ht="13.5" customHeight="1">
-      <c r="A56" s="49"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
+      <c r="A56" s="46"/>
+      <c r="I56" s="77"/>
     </row>
     <row r="57" ht="13.5" customHeight="1">
-      <c r="A57" s="49"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="7"/>
+      <c r="A57" s="46"/>
+      <c r="I57" s="77"/>
     </row>
     <row r="58" ht="13.5" customHeight="1">
-      <c r="A58" s="49"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
+      <c r="A58" s="46"/>
+      <c r="I58" s="77"/>
     </row>
     <row r="59" ht="13.5" customHeight="1">
-      <c r="A59" s="49"/>
-      <c r="I59" s="7"/>
-      <c r="J59" s="7"/>
+      <c r="A59" s="46"/>
+      <c r="I59" s="77"/>
     </row>
     <row r="60" ht="13.5" customHeight="1">
-      <c r="A60" s="49"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="7"/>
+      <c r="A60" s="46"/>
+      <c r="I60" s="77"/>
     </row>
     <row r="61" ht="13.5" customHeight="1">
-      <c r="A61" s="49"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="7"/>
+      <c r="A61" s="46"/>
+      <c r="I61" s="77"/>
     </row>
     <row r="62" ht="13.5" customHeight="1">
-      <c r="A62" s="49"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="7"/>
+      <c r="A62" s="46"/>
+      <c r="I62" s="77"/>
     </row>
     <row r="63" ht="13.5" customHeight="1">
-      <c r="A63" s="49"/>
-      <c r="I63" s="7"/>
-      <c r="J63" s="7"/>
+      <c r="A63" s="46"/>
+      <c r="I63" s="77"/>
     </row>
     <row r="64" ht="13.5" customHeight="1">
-      <c r="A64" s="49"/>
-      <c r="I64" s="7"/>
-      <c r="J64" s="7"/>
+      <c r="A64" s="46"/>
+      <c r="I64" s="77"/>
     </row>
     <row r="65" ht="13.5" customHeight="1">
-      <c r="A65" s="49"/>
-      <c r="I65" s="7"/>
-      <c r="J65" s="7"/>
+      <c r="A65" s="46"/>
+      <c r="I65" s="77"/>
     </row>
     <row r="66" ht="13.5" customHeight="1">
-      <c r="A66" s="49"/>
-      <c r="I66" s="7"/>
-      <c r="J66" s="7"/>
+      <c r="A66" s="46"/>
+      <c r="I66" s="77"/>
     </row>
     <row r="67" ht="13.5" customHeight="1">
-      <c r="A67" s="49"/>
-      <c r="I67" s="7"/>
-      <c r="J67" s="7"/>
+      <c r="A67" s="46"/>
+      <c r="I67" s="77"/>
     </row>
     <row r="68" ht="13.5" customHeight="1">
-      <c r="A68" s="49"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="7"/>
+      <c r="A68" s="46"/>
+      <c r="I68" s="77"/>
     </row>
     <row r="69" ht="13.5" customHeight="1">
-      <c r="A69" s="49"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="7"/>
+      <c r="A69" s="46"/>
+      <c r="I69" s="77"/>
     </row>
     <row r="70" ht="13.5" customHeight="1">
-      <c r="A70" s="49"/>
-      <c r="I70" s="7"/>
-      <c r="J70" s="7"/>
+      <c r="A70" s="46"/>
+      <c r="I70" s="77"/>
     </row>
     <row r="71" ht="13.5" customHeight="1">
-      <c r="A71" s="49"/>
-      <c r="I71" s="7"/>
-      <c r="J71" s="7"/>
+      <c r="A71" s="46"/>
+      <c r="I71" s="77"/>
     </row>
     <row r="72" ht="13.5" customHeight="1">
-      <c r="A72" s="49"/>
-      <c r="I72" s="7"/>
-      <c r="J72" s="7"/>
+      <c r="A72" s="46"/>
+      <c r="I72" s="77"/>
     </row>
     <row r="73" ht="13.5" customHeight="1">
-      <c r="A73" s="49"/>
-      <c r="I73" s="7"/>
-      <c r="J73" s="7"/>
+      <c r="A73" s="46"/>
+      <c r="I73" s="77"/>
     </row>
     <row r="74" ht="13.5" customHeight="1">
-      <c r="A74" s="49"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
+      <c r="A74" s="46"/>
+      <c r="I74" s="77"/>
     </row>
     <row r="75" ht="13.5" customHeight="1">
-      <c r="A75" s="49"/>
-      <c r="I75" s="7"/>
-      <c r="J75" s="7"/>
+      <c r="A75" s="46"/>
+      <c r="I75" s="77"/>
     </row>
     <row r="76" ht="13.5" customHeight="1">
-      <c r="A76" s="49"/>
-      <c r="I76" s="7"/>
-      <c r="J76" s="7"/>
+      <c r="A76" s="46"/>
+      <c r="I76" s="77"/>
     </row>
     <row r="77" ht="13.5" customHeight="1">
-      <c r="A77" s="49"/>
-      <c r="I77" s="7"/>
-      <c r="J77" s="7"/>
+      <c r="A77" s="46"/>
+      <c r="I77" s="77"/>
     </row>
     <row r="78" ht="13.5" customHeight="1">
-      <c r="A78" s="49"/>
-      <c r="I78" s="7"/>
-      <c r="J78" s="7"/>
+      <c r="A78" s="46"/>
+      <c r="I78" s="77"/>
     </row>
     <row r="79" ht="13.5" customHeight="1">
-      <c r="A79" s="49"/>
-      <c r="I79" s="7"/>
-      <c r="J79" s="7"/>
+      <c r="A79" s="46"/>
+      <c r="I79" s="77"/>
     </row>
     <row r="80" ht="13.5" customHeight="1">
-      <c r="A80" s="49"/>
-      <c r="I80" s="7"/>
-      <c r="J80" s="7"/>
+      <c r="A80" s="46"/>
+      <c r="I80" s="77"/>
     </row>
     <row r="81" ht="13.5" customHeight="1">
-      <c r="A81" s="49"/>
-      <c r="I81" s="7"/>
-      <c r="J81" s="7"/>
+      <c r="A81" s="46"/>
+      <c r="I81" s="77"/>
     </row>
     <row r="82" ht="13.5" customHeight="1">
-      <c r="A82" s="49"/>
-      <c r="I82" s="7"/>
-      <c r="J82" s="7"/>
+      <c r="A82" s="46"/>
+      <c r="I82" s="77"/>
     </row>
     <row r="83" ht="13.5" customHeight="1">
-      <c r="A83" s="49"/>
-      <c r="I83" s="7"/>
-      <c r="J83" s="7"/>
+      <c r="A83" s="46"/>
+      <c r="I83" s="77"/>
     </row>
     <row r="84" ht="13.5" customHeight="1">
-      <c r="A84" s="49"/>
-      <c r="I84" s="7"/>
-      <c r="J84" s="7"/>
+      <c r="A84" s="46"/>
+      <c r="I84" s="77"/>
     </row>
     <row r="85" ht="13.5" customHeight="1">
-      <c r="A85" s="49"/>
-      <c r="I85" s="7"/>
-      <c r="J85" s="7"/>
+      <c r="A85" s="46"/>
+      <c r="I85" s="77"/>
     </row>
     <row r="86" ht="13.5" customHeight="1">
-      <c r="A86" s="49"/>
-      <c r="I86" s="7"/>
-      <c r="J86" s="7"/>
+      <c r="A86" s="46"/>
+      <c r="I86" s="77"/>
     </row>
     <row r="87" ht="13.5" customHeight="1">
-      <c r="A87" s="49"/>
-      <c r="I87" s="7"/>
-      <c r="J87" s="7"/>
+      <c r="A87" s="46"/>
+      <c r="I87" s="77"/>
     </row>
     <row r="88" ht="13.5" customHeight="1">
-      <c r="A88" s="49"/>
-      <c r="I88" s="7"/>
-      <c r="J88" s="7"/>
+      <c r="A88" s="46"/>
+      <c r="I88" s="77"/>
     </row>
     <row r="89" ht="13.5" customHeight="1">
-      <c r="A89" s="49"/>
-      <c r="I89" s="7"/>
-      <c r="J89" s="7"/>
+      <c r="A89" s="46"/>
+      <c r="I89" s="77"/>
     </row>
     <row r="90" ht="13.5" customHeight="1">
-      <c r="A90" s="49"/>
-      <c r="I90" s="7"/>
-      <c r="J90" s="7"/>
+      <c r="A90" s="46"/>
+      <c r="I90" s="77"/>
     </row>
     <row r="91" ht="13.5" customHeight="1">
-      <c r="A91" s="49"/>
-      <c r="I91" s="7"/>
-      <c r="J91" s="7"/>
+      <c r="A91" s="46"/>
+      <c r="I91" s="77"/>
     </row>
     <row r="92" ht="13.5" customHeight="1">
-      <c r="A92" s="49"/>
-      <c r="I92" s="7"/>
-      <c r="J92" s="7"/>
+      <c r="A92" s="46"/>
+      <c r="I92" s="77"/>
     </row>
     <row r="93" ht="13.5" customHeight="1">
-      <c r="A93" s="49"/>
-      <c r="I93" s="7"/>
-      <c r="J93" s="7"/>
+      <c r="A93" s="46"/>
+      <c r="I93" s="77"/>
     </row>
     <row r="94" ht="13.5" customHeight="1">
-      <c r="A94" s="49"/>
-      <c r="I94" s="7"/>
-      <c r="J94" s="7"/>
+      <c r="A94" s="46"/>
+      <c r="I94" s="77"/>
     </row>
     <row r="95" ht="13.5" customHeight="1">
-      <c r="A95" s="49"/>
-      <c r="I95" s="7"/>
-      <c r="J95" s="7"/>
+      <c r="A95" s="46"/>
+      <c r="I95" s="77"/>
     </row>
     <row r="96" ht="13.5" customHeight="1">
-      <c r="A96" s="49"/>
-      <c r="I96" s="7"/>
-      <c r="J96" s="7"/>
+      <c r="A96" s="46"/>
+      <c r="I96" s="77"/>
     </row>
     <row r="97" ht="13.5" customHeight="1">
-      <c r="A97" s="49"/>
-      <c r="I97" s="7"/>
-      <c r="J97" s="7"/>
+      <c r="A97" s="46"/>
+      <c r="I97" s="77"/>
     </row>
     <row r="98" ht="13.5" customHeight="1">
-      <c r="A98" s="49"/>
-      <c r="I98" s="7"/>
-      <c r="J98" s="7"/>
+      <c r="A98" s="46"/>
+      <c r="I98" s="77"/>
     </row>
     <row r="99" ht="13.5" customHeight="1">
-      <c r="A99" s="49"/>
-      <c r="I99" s="7"/>
-      <c r="J99" s="7"/>
+      <c r="A99" s="46"/>
+      <c r="I99" s="77"/>
     </row>
     <row r="100" ht="13.5" customHeight="1">
-      <c r="A100" s="49"/>
-      <c r="I100" s="7"/>
-      <c r="J100" s="7"/>
+      <c r="A100" s="46"/>
+      <c r="I100" s="77"/>
     </row>
     <row r="101" ht="13.5" customHeight="1">
-      <c r="A101" s="49"/>
-      <c r="I101" s="7"/>
-      <c r="J101" s="7"/>
+      <c r="A101" s="46"/>
+      <c r="I101" s="77"/>
     </row>
     <row r="102" ht="13.5" customHeight="1">
-      <c r="A102" s="49"/>
-      <c r="I102" s="7"/>
-      <c r="J102" s="7"/>
+      <c r="A102" s="46"/>
+      <c r="I102" s="77"/>
     </row>
     <row r="103" ht="13.5" customHeight="1">
-      <c r="A103" s="49"/>
-      <c r="I103" s="7"/>
-      <c r="J103" s="7"/>
+      <c r="A103" s="46"/>
+      <c r="I103" s="77"/>
     </row>
     <row r="104" ht="13.5" customHeight="1">
-      <c r="A104" s="49"/>
-      <c r="I104" s="7"/>
-      <c r="J104" s="7"/>
+      <c r="A104" s="46"/>
+      <c r="I104" s="77"/>
     </row>
     <row r="105" ht="13.5" customHeight="1">
-      <c r="A105" s="49"/>
-      <c r="I105" s="7"/>
-      <c r="J105" s="7"/>
+      <c r="A105" s="46"/>
+      <c r="I105" s="77"/>
     </row>
     <row r="106" ht="13.5" customHeight="1">
-      <c r="A106" s="49"/>
-      <c r="I106" s="7"/>
-      <c r="J106" s="7"/>
+      <c r="A106" s="46"/>
+      <c r="I106" s="77"/>
     </row>
     <row r="107" ht="13.5" customHeight="1">
-      <c r="A107" s="49"/>
-      <c r="I107" s="7"/>
-      <c r="J107" s="7"/>
+      <c r="A107" s="46"/>
+      <c r="I107" s="77"/>
     </row>
     <row r="108" ht="13.5" customHeight="1">
-      <c r="A108" s="49"/>
-      <c r="I108" s="7"/>
-      <c r="J108" s="7"/>
+      <c r="A108" s="46"/>
+      <c r="I108" s="77"/>
     </row>
     <row r="109" ht="13.5" customHeight="1">
-      <c r="A109" s="49"/>
-      <c r="I109" s="7"/>
-      <c r="J109" s="7"/>
+      <c r="A109" s="46"/>
+      <c r="I109" s="77"/>
     </row>
     <row r="110" ht="13.5" customHeight="1">
-      <c r="A110" s="49"/>
-      <c r="I110" s="7"/>
-      <c r="J110" s="7"/>
+      <c r="A110" s="46"/>
+      <c r="I110" s="77"/>
     </row>
     <row r="111" ht="13.5" customHeight="1">
-      <c r="A111" s="49"/>
-      <c r="I111" s="7"/>
-      <c r="J111" s="7"/>
+      <c r="A111" s="46"/>
+      <c r="I111" s="77"/>
     </row>
     <row r="112" ht="13.5" customHeight="1">
-      <c r="A112" s="49"/>
-      <c r="I112" s="7"/>
-      <c r="J112" s="7"/>
+      <c r="A112" s="46"/>
+      <c r="I112" s="77"/>
     </row>
     <row r="113" ht="13.5" customHeight="1">
-      <c r="A113" s="49"/>
-      <c r="I113" s="7"/>
-      <c r="J113" s="7"/>
+      <c r="A113" s="46"/>
+      <c r="I113" s="77"/>
     </row>
     <row r="114" ht="13.5" customHeight="1">
-      <c r="A114" s="49"/>
-      <c r="I114" s="7"/>
-      <c r="J114" s="7"/>
+      <c r="A114" s="46"/>
+      <c r="I114" s="77"/>
     </row>
     <row r="115" ht="13.5" customHeight="1">
-      <c r="A115" s="49"/>
-      <c r="I115" s="7"/>
-      <c r="J115" s="7"/>
+      <c r="A115" s="46"/>
+      <c r="I115" s="77"/>
     </row>
     <row r="116" ht="13.5" customHeight="1">
-      <c r="A116" s="49"/>
-      <c r="I116" s="7"/>
-      <c r="J116" s="7"/>
+      <c r="A116" s="46"/>
+      <c r="I116" s="77"/>
     </row>
     <row r="117" ht="13.5" customHeight="1">
-      <c r="A117" s="49"/>
-      <c r="I117" s="7"/>
-      <c r="J117" s="7"/>
+      <c r="A117" s="46"/>
+      <c r="I117" s="77"/>
     </row>
     <row r="118" ht="13.5" customHeight="1">
-      <c r="A118" s="49"/>
-      <c r="I118" s="7"/>
-      <c r="J118" s="7"/>
+      <c r="A118" s="46"/>
+      <c r="I118" s="77"/>
     </row>
     <row r="119" ht="13.5" customHeight="1">
-      <c r="A119" s="49"/>
-      <c r="I119" s="7"/>
-      <c r="J119" s="7"/>
+      <c r="A119" s="46"/>
+      <c r="I119" s="77"/>
     </row>
     <row r="120" ht="13.5" customHeight="1">
-      <c r="A120" s="49"/>
-      <c r="I120" s="7"/>
-      <c r="J120" s="7"/>
+      <c r="A120" s="46"/>
+      <c r="I120" s="77"/>
     </row>
     <row r="121" ht="13.5" customHeight="1">
-      <c r="A121" s="49"/>
-      <c r="I121" s="7"/>
-      <c r="J121" s="7"/>
+      <c r="A121" s="46"/>
+      <c r="I121" s="77"/>
     </row>
     <row r="122" ht="13.5" customHeight="1">
-      <c r="A122" s="49"/>
-      <c r="I122" s="7"/>
-      <c r="J122" s="7"/>
+      <c r="A122" s="46"/>
+      <c r="I122" s="77"/>
     </row>
     <row r="123" ht="13.5" customHeight="1">
-      <c r="A123" s="49"/>
-      <c r="I123" s="7"/>
-      <c r="J123" s="7"/>
+      <c r="A123" s="46"/>
+      <c r="I123" s="77"/>
     </row>
     <row r="124" ht="13.5" customHeight="1">
-      <c r="A124" s="49"/>
-      <c r="I124" s="7"/>
-      <c r="J124" s="7"/>
+      <c r="A124" s="46"/>
+      <c r="I124" s="77"/>
     </row>
     <row r="125" ht="13.5" customHeight="1">
-      <c r="A125" s="49"/>
-      <c r="I125" s="7"/>
-      <c r="J125" s="7"/>
+      <c r="A125" s="46"/>
+      <c r="I125" s="77"/>
     </row>
     <row r="126" ht="13.5" customHeight="1">
-      <c r="A126" s="49"/>
-      <c r="I126" s="7"/>
-      <c r="J126" s="7"/>
+      <c r="A126" s="46"/>
+      <c r="I126" s="77"/>
     </row>
     <row r="127" ht="13.5" customHeight="1">
-      <c r="A127" s="49"/>
-      <c r="I127" s="7"/>
-      <c r="J127" s="7"/>
+      <c r="A127" s="46"/>
+      <c r="I127" s="77"/>
     </row>
     <row r="128" ht="13.5" customHeight="1">
-      <c r="A128" s="49"/>
-      <c r="I128" s="7"/>
-      <c r="J128" s="7"/>
+      <c r="A128" s="46"/>
+      <c r="I128" s="77"/>
     </row>
     <row r="129" ht="13.5" customHeight="1">
-      <c r="A129" s="49"/>
-      <c r="I129" s="7"/>
-      <c r="J129" s="7"/>
+      <c r="A129" s="46"/>
+      <c r="I129" s="77"/>
     </row>
     <row r="130" ht="13.5" customHeight="1">
-      <c r="A130" s="49"/>
-      <c r="I130" s="7"/>
-      <c r="J130" s="7"/>
+      <c r="A130" s="46"/>
+      <c r="I130" s="77"/>
     </row>
     <row r="131" ht="13.5" customHeight="1">
-      <c r="A131" s="49"/>
-      <c r="I131" s="7"/>
-      <c r="J131" s="7"/>
+      <c r="A131" s="46"/>
+      <c r="I131" s="77"/>
     </row>
     <row r="132" ht="13.5" customHeight="1">
-      <c r="A132" s="49"/>
-      <c r="I132" s="7"/>
-      <c r="J132" s="7"/>
+      <c r="A132" s="46"/>
+      <c r="I132" s="77"/>
     </row>
     <row r="133" ht="13.5" customHeight="1">
-      <c r="A133" s="49"/>
-      <c r="I133" s="7"/>
-      <c r="J133" s="7"/>
+      <c r="A133" s="46"/>
+      <c r="I133" s="77"/>
     </row>
     <row r="134" ht="13.5" customHeight="1">
-      <c r="A134" s="49"/>
-      <c r="I134" s="7"/>
-      <c r="J134" s="7"/>
+      <c r="A134" s="46"/>
+      <c r="I134" s="77"/>
     </row>
     <row r="135" ht="13.5" customHeight="1">
-      <c r="A135" s="49"/>
-      <c r="I135" s="7"/>
-      <c r="J135" s="7"/>
+      <c r="A135" s="46"/>
+      <c r="I135" s="77"/>
     </row>
     <row r="136" ht="13.5" customHeight="1">
-      <c r="A136" s="49"/>
-      <c r="I136" s="7"/>
-      <c r="J136" s="7"/>
+      <c r="A136" s="46"/>
+      <c r="I136" s="77"/>
     </row>
     <row r="137" ht="13.5" customHeight="1">
-      <c r="A137" s="49"/>
-      <c r="I137" s="7"/>
-      <c r="J137" s="7"/>
+      <c r="A137" s="46"/>
+      <c r="I137" s="77"/>
     </row>
     <row r="138" ht="13.5" customHeight="1">
-      <c r="A138" s="49"/>
-      <c r="I138" s="7"/>
-      <c r="J138" s="7"/>
+      <c r="A138" s="46"/>
+      <c r="I138" s="77"/>
     </row>
     <row r="139" ht="13.5" customHeight="1">
-      <c r="A139" s="49"/>
-      <c r="I139" s="7"/>
-      <c r="J139" s="7"/>
+      <c r="A139" s="46"/>
+      <c r="I139" s="77"/>
     </row>
     <row r="140" ht="13.5" customHeight="1">
-      <c r="A140" s="49"/>
-      <c r="I140" s="7"/>
-      <c r="J140" s="7"/>
+      <c r="A140" s="46"/>
+      <c r="I140" s="77"/>
     </row>
     <row r="141" ht="13.5" customHeight="1">
-      <c r="A141" s="49"/>
-      <c r="I141" s="7"/>
-      <c r="J141" s="7"/>
+      <c r="A141" s="46"/>
+      <c r="I141" s="77"/>
     </row>
     <row r="142" ht="13.5" customHeight="1">
-      <c r="A142" s="49"/>
-      <c r="I142" s="7"/>
-      <c r="J142" s="7"/>
+      <c r="A142" s="46"/>
+      <c r="I142" s="77"/>
     </row>
     <row r="143" ht="13.5" customHeight="1">
-      <c r="A143" s="49"/>
-      <c r="I143" s="7"/>
-      <c r="J143" s="7"/>
+      <c r="A143" s="46"/>
+      <c r="I143" s="77"/>
     </row>
     <row r="144" ht="13.5" customHeight="1">
-      <c r="A144" s="49"/>
-      <c r="I144" s="7"/>
-      <c r="J144" s="7"/>
+      <c r="A144" s="46"/>
+      <c r="I144" s="77"/>
     </row>
     <row r="145" ht="13.5" customHeight="1">
-      <c r="A145" s="49"/>
-      <c r="I145" s="7"/>
-      <c r="J145" s="7"/>
+      <c r="A145" s="46"/>
+      <c r="I145" s="77"/>
     </row>
     <row r="146" ht="13.5" customHeight="1">
-      <c r="A146" s="49"/>
-      <c r="I146" s="7"/>
-      <c r="J146" s="7"/>
+      <c r="A146" s="46"/>
+      <c r="I146" s="77"/>
     </row>
     <row r="147" ht="13.5" customHeight="1">
-      <c r="A147" s="49"/>
-      <c r="I147" s="7"/>
-      <c r="J147" s="7"/>
+      <c r="A147" s="46"/>
+      <c r="I147" s="77"/>
     </row>
     <row r="148" ht="13.5" customHeight="1">
-      <c r="A148" s="49"/>
-      <c r="I148" s="7"/>
-      <c r="J148" s="7"/>
+      <c r="A148" s="46"/>
+      <c r="I148" s="77"/>
     </row>
     <row r="149" ht="13.5" customHeight="1">
-      <c r="A149" s="49"/>
-      <c r="I149" s="7"/>
-      <c r="J149" s="7"/>
+      <c r="A149" s="46"/>
+      <c r="I149" s="77"/>
     </row>
     <row r="150" ht="13.5" customHeight="1">
-      <c r="A150" s="49"/>
-      <c r="I150" s="7"/>
-      <c r="J150" s="7"/>
+      <c r="A150" s="46"/>
+      <c r="I150" s="77"/>
     </row>
     <row r="151" ht="13.5" customHeight="1">
-      <c r="A151" s="49"/>
-      <c r="I151" s="7"/>
-      <c r="J151" s="7"/>
+      <c r="A151" s="46"/>
+      <c r="I151" s="77"/>
     </row>
     <row r="152" ht="13.5" customHeight="1">
-      <c r="A152" s="49"/>
-      <c r="I152" s="7"/>
-      <c r="J152" s="7"/>
+      <c r="A152" s="46"/>
+      <c r="I152" s="77"/>
     </row>
     <row r="153" ht="13.5" customHeight="1">
-      <c r="A153" s="49"/>
-      <c r="I153" s="7"/>
-      <c r="J153" s="7"/>
+      <c r="A153" s="46"/>
+      <c r="I153" s="77"/>
     </row>
     <row r="154" ht="13.5" customHeight="1">
-      <c r="A154" s="49"/>
-      <c r="I154" s="7"/>
-      <c r="J154" s="7"/>
+      <c r="A154" s="46"/>
+      <c r="I154" s="77"/>
     </row>
     <row r="155" ht="13.5" customHeight="1">
-      <c r="A155" s="49"/>
-      <c r="I155" s="7"/>
-      <c r="J155" s="7"/>
+      <c r="A155" s="46"/>
+      <c r="I155" s="77"/>
     </row>
     <row r="156" ht="13.5" customHeight="1">
-      <c r="A156" s="49"/>
-      <c r="I156" s="7"/>
-      <c r="J156" s="7"/>
+      <c r="A156" s="46"/>
+      <c r="I156" s="77"/>
     </row>
     <row r="157" ht="13.5" customHeight="1">
-      <c r="A157" s="49"/>
-      <c r="I157" s="7"/>
-      <c r="J157" s="7"/>
+      <c r="A157" s="46"/>
+      <c r="I157" s="77"/>
     </row>
     <row r="158" ht="13.5" customHeight="1">
-      <c r="A158" s="49"/>
-      <c r="I158" s="7"/>
-      <c r="J158" s="7"/>
+      <c r="A158" s="46"/>
+      <c r="I158" s="77"/>
     </row>
     <row r="159" ht="13.5" customHeight="1">
-      <c r="A159" s="49"/>
-      <c r="I159" s="7"/>
-      <c r="J159" s="7"/>
+      <c r="A159" s="46"/>
+      <c r="I159" s="77"/>
     </row>
     <row r="160" ht="13.5" customHeight="1">
-      <c r="A160" s="49"/>
-      <c r="I160" s="7"/>
-      <c r="J160" s="7"/>
+      <c r="A160" s="46"/>
+      <c r="I160" s="77"/>
     </row>
     <row r="161" ht="13.5" customHeight="1">
-      <c r="A161" s="49"/>
-      <c r="I161" s="7"/>
-      <c r="J161" s="7"/>
+      <c r="A161" s="46"/>
+      <c r="I161" s="77"/>
     </row>
     <row r="162" ht="13.5" customHeight="1">
-      <c r="A162" s="49"/>
-      <c r="I162" s="7"/>
-      <c r="J162" s="7"/>
+      <c r="A162" s="46"/>
+      <c r="I162" s="77"/>
     </row>
     <row r="163" ht="13.5" customHeight="1">
-      <c r="A163" s="49"/>
-      <c r="I163" s="7"/>
-      <c r="J163" s="7"/>
+      <c r="A163" s="46"/>
+      <c r="I163" s="77"/>
     </row>
     <row r="164" ht="13.5" customHeight="1">
-      <c r="A164" s="49"/>
-      <c r="I164" s="7"/>
-      <c r="J164" s="7"/>
+      <c r="A164" s="46"/>
+      <c r="I164" s="77"/>
     </row>
     <row r="165" ht="13.5" customHeight="1">
-      <c r="A165" s="49"/>
-      <c r="I165" s="7"/>
-      <c r="J165" s="7"/>
+      <c r="A165" s="46"/>
+      <c r="I165" s="77"/>
     </row>
     <row r="166" ht="13.5" customHeight="1">
-      <c r="A166" s="49"/>
-      <c r="I166" s="7"/>
-      <c r="J166" s="7"/>
+      <c r="A166" s="46"/>
+      <c r="I166" s="77"/>
     </row>
     <row r="167" ht="13.5" customHeight="1">
-      <c r="A167" s="49"/>
-      <c r="I167" s="7"/>
-      <c r="J167" s="7"/>
+      <c r="A167" s="46"/>
+      <c r="I167" s="77"/>
     </row>
     <row r="168" ht="13.5" customHeight="1">
-      <c r="A168" s="49"/>
-      <c r="I168" s="7"/>
-      <c r="J168" s="7"/>
+      <c r="A168" s="46"/>
+      <c r="I168" s="77"/>
     </row>
     <row r="169" ht="13.5" customHeight="1">
-      <c r="A169" s="49"/>
-      <c r="I169" s="7"/>
-      <c r="J169" s="7"/>
+      <c r="A169" s="46"/>
+      <c r="I169" s="77"/>
     </row>
     <row r="170" ht="13.5" customHeight="1">
-      <c r="A170" s="49"/>
-      <c r="I170" s="7"/>
-      <c r="J170" s="7"/>
+      <c r="A170" s="46"/>
+      <c r="I170" s="77"/>
     </row>
     <row r="171" ht="13.5" customHeight="1">
-      <c r="A171" s="49"/>
-      <c r="I171" s="7"/>
-      <c r="J171" s="7"/>
+      <c r="A171" s="46"/>
+      <c r="I171" s="77"/>
     </row>
     <row r="172" ht="13.5" customHeight="1">
-      <c r="A172" s="49"/>
-      <c r="I172" s="7"/>
-      <c r="J172" s="7"/>
+      <c r="A172" s="46"/>
+      <c r="I172" s="77"/>
     </row>
     <row r="173" ht="13.5" customHeight="1">
-      <c r="A173" s="49"/>
-      <c r="I173" s="7"/>
-      <c r="J173" s="7"/>
+      <c r="A173" s="46"/>
+      <c r="I173" s="77"/>
     </row>
     <row r="174" ht="13.5" customHeight="1">
-      <c r="A174" s="49"/>
-      <c r="I174" s="7"/>
-      <c r="J174" s="7"/>
+      <c r="A174" s="46"/>
+      <c r="I174" s="77"/>
     </row>
     <row r="175" ht="13.5" customHeight="1">
-      <c r="A175" s="49"/>
-      <c r="I175" s="7"/>
-      <c r="J175" s="7"/>
+      <c r="A175" s="46"/>
+      <c r="I175" s="77"/>
     </row>
     <row r="176" ht="13.5" customHeight="1">
-      <c r="A176" s="49"/>
-      <c r="I176" s="7"/>
-      <c r="J176" s="7"/>
+      <c r="A176" s="46"/>
+      <c r="I176" s="77"/>
     </row>
     <row r="177" ht="13.5" customHeight="1">
-      <c r="A177" s="49"/>
-      <c r="I177" s="7"/>
-      <c r="J177" s="7"/>
+      <c r="A177" s="46"/>
+      <c r="I177" s="77"/>
     </row>
     <row r="178" ht="13.5" customHeight="1">
-      <c r="A178" s="49"/>
-      <c r="I178" s="7"/>
-      <c r="J178" s="7"/>
+      <c r="A178" s="46"/>
+      <c r="I178" s="77"/>
     </row>
     <row r="179" ht="13.5" customHeight="1">
-      <c r="A179" s="49"/>
-      <c r="I179" s="7"/>
-      <c r="J179" s="7"/>
+      <c r="A179" s="46"/>
+      <c r="I179" s="77"/>
     </row>
     <row r="180" ht="13.5" customHeight="1">
-      <c r="A180" s="49"/>
-      <c r="I180" s="7"/>
-      <c r="J180" s="7"/>
+      <c r="A180" s="46"/>
+      <c r="I180" s="77"/>
     </row>
     <row r="181" ht="13.5" customHeight="1">
-      <c r="A181" s="49"/>
-      <c r="I181" s="7"/>
-      <c r="J181" s="7"/>
+      <c r="A181" s="46"/>
+      <c r="I181" s="77"/>
     </row>
     <row r="182" ht="13.5" customHeight="1">
-      <c r="A182" s="49"/>
-      <c r="I182" s="7"/>
-      <c r="J182" s="7"/>
+      <c r="A182" s="46"/>
+      <c r="I182" s="77"/>
     </row>
     <row r="183" ht="13.5" customHeight="1">
-      <c r="A183" s="49"/>
-      <c r="I183" s="7"/>
-      <c r="J183" s="7"/>
+      <c r="A183" s="46"/>
+      <c r="I183" s="77"/>
     </row>
     <row r="184" ht="13.5" customHeight="1">
-      <c r="A184" s="49"/>
-      <c r="I184" s="7"/>
-      <c r="J184" s="7"/>
+      <c r="A184" s="46"/>
+      <c r="I184" s="77"/>
     </row>
     <row r="185" ht="13.5" customHeight="1">
-      <c r="A185" s="49"/>
-      <c r="I185" s="7"/>
-      <c r="J185" s="7"/>
+      <c r="A185" s="46"/>
+      <c r="I185" s="77"/>
     </row>
     <row r="186" ht="13.5" customHeight="1">
-      <c r="A186" s="49"/>
-      <c r="I186" s="7"/>
-      <c r="J186" s="7"/>
+      <c r="A186" s="46"/>
+      <c r="I186" s="77"/>
     </row>
     <row r="187" ht="13.5" customHeight="1">
-      <c r="A187" s="49"/>
-      <c r="I187" s="7"/>
-      <c r="J187" s="7"/>
+      <c r="A187" s="46"/>
+      <c r="I187" s="77"/>
     </row>
     <row r="188" ht="13.5" customHeight="1">
-      <c r="A188" s="49"/>
-      <c r="I188" s="7"/>
-      <c r="J188" s="7"/>
+      <c r="A188" s="46"/>
+      <c r="I188" s="77"/>
     </row>
     <row r="189" ht="13.5" customHeight="1">
-      <c r="A189" s="49"/>
-      <c r="I189" s="7"/>
-      <c r="J189" s="7"/>
+      <c r="A189" s="46"/>
+      <c r="I189" s="77"/>
     </row>
     <row r="190" ht="13.5" customHeight="1">
-      <c r="A190" s="49"/>
-      <c r="I190" s="7"/>
-      <c r="J190" s="7"/>
+      <c r="A190" s="46"/>
+      <c r="I190" s="77"/>
     </row>
     <row r="191" ht="13.5" customHeight="1">
-      <c r="A191" s="49"/>
-      <c r="I191" s="7"/>
-      <c r="J191" s="7"/>
+      <c r="A191" s="46"/>
+      <c r="I191" s="77"/>
     </row>
     <row r="192" ht="13.5" customHeight="1">
-      <c r="A192" s="49"/>
-      <c r="I192" s="7"/>
-      <c r="J192" s="7"/>
+      <c r="A192" s="46"/>
+      <c r="I192" s="77"/>
     </row>
     <row r="193" ht="13.5" customHeight="1">
-      <c r="A193" s="49"/>
-      <c r="I193" s="7"/>
-      <c r="J193" s="7"/>
+      <c r="A193" s="46"/>
+      <c r="I193" s="77"/>
     </row>
     <row r="194" ht="13.5" customHeight="1">
-      <c r="A194" s="49"/>
-      <c r="I194" s="7"/>
-      <c r="J194" s="7"/>
+      <c r="A194" s="46"/>
+      <c r="I194" s="77"/>
     </row>
     <row r="195" ht="13.5" customHeight="1">
-      <c r="A195" s="49"/>
-      <c r="I195" s="7"/>
-      <c r="J195" s="7"/>
+      <c r="A195" s="46"/>
+      <c r="I195" s="77"/>
     </row>
     <row r="196" ht="13.5" customHeight="1">
-      <c r="A196" s="49"/>
-      <c r="I196" s="7"/>
-      <c r="J196" s="7"/>
+      <c r="A196" s="46"/>
+      <c r="I196" s="77"/>
     </row>
     <row r="197" ht="13.5" customHeight="1">
-      <c r="A197" s="49"/>
-      <c r="I197" s="7"/>
-      <c r="J197" s="7"/>
+      <c r="A197" s="46"/>
+      <c r="I197" s="77"/>
     </row>
     <row r="198" ht="13.5" customHeight="1">
-      <c r="A198" s="49"/>
-      <c r="I198" s="7"/>
-      <c r="J198" s="7"/>
+      <c r="A198" s="46"/>
+      <c r="I198" s="77"/>
     </row>
     <row r="199" ht="13.5" customHeight="1">
-      <c r="A199" s="49"/>
-      <c r="I199" s="7"/>
-      <c r="J199" s="7"/>
+      <c r="A199" s="46"/>
+      <c r="I199" s="77"/>
     </row>
     <row r="200" ht="13.5" customHeight="1">
-      <c r="A200" s="49"/>
-      <c r="I200" s="7"/>
-      <c r="J200" s="7"/>
+      <c r="A200" s="46"/>
+      <c r="I200" s="77"/>
     </row>
     <row r="201" ht="13.5" customHeight="1">
-      <c r="A201" s="49"/>
-      <c r="I201" s="7"/>
-      <c r="J201" s="7"/>
+      <c r="A201" s="46"/>
+      <c r="I201" s="77"/>
     </row>
     <row r="202" ht="13.5" customHeight="1">
-      <c r="A202" s="49"/>
-      <c r="I202" s="7"/>
-      <c r="J202" s="7"/>
+      <c r="A202" s="46"/>
+      <c r="I202" s="77"/>
     </row>
     <row r="203" ht="13.5" customHeight="1">
-      <c r="A203" s="49"/>
-      <c r="I203" s="7"/>
-      <c r="J203" s="7"/>
+      <c r="A203" s="46"/>
+      <c r="I203" s="77"/>
     </row>
     <row r="204" ht="13.5" customHeight="1">
-      <c r="A204" s="49"/>
-      <c r="I204" s="7"/>
-      <c r="J204" s="7"/>
+      <c r="A204" s="46"/>
+      <c r="I204" s="77"/>
     </row>
     <row r="205" ht="13.5" customHeight="1">
-      <c r="A205" s="49"/>
-      <c r="I205" s="7"/>
-      <c r="J205" s="7"/>
+      <c r="A205" s="46"/>
+      <c r="I205" s="77"/>
     </row>
     <row r="206" ht="13.5" customHeight="1">
-      <c r="A206" s="49"/>
-      <c r="I206" s="7"/>
-      <c r="J206" s="7"/>
+      <c r="A206" s="46"/>
+      <c r="I206" s="77"/>
     </row>
     <row r="207" ht="13.5" customHeight="1">
-      <c r="A207" s="49"/>
-      <c r="I207" s="7"/>
-      <c r="J207" s="7"/>
+      <c r="A207" s="46"/>
+      <c r="I207" s="77"/>
     </row>
     <row r="208" ht="13.5" customHeight="1">
-      <c r="A208" s="49"/>
-      <c r="I208" s="7"/>
-      <c r="J208" s="7"/>
+      <c r="A208" s="46"/>
+      <c r="I208" s="77"/>
     </row>
     <row r="209" ht="13.5" customHeight="1">
-      <c r="A209" s="49"/>
-      <c r="I209" s="7"/>
-      <c r="J209" s="7"/>
+      <c r="A209" s="46"/>
+      <c r="I209" s="77"/>
     </row>
     <row r="210" ht="13.5" customHeight="1">
-      <c r="A210" s="49"/>
-      <c r="I210" s="7"/>
-      <c r="J210" s="7"/>
+      <c r="A210" s="46"/>
+      <c r="I210" s="77"/>
     </row>
     <row r="211" ht="13.5" customHeight="1">
-      <c r="A211" s="49"/>
-      <c r="I211" s="7"/>
-      <c r="J211" s="7"/>
+      <c r="A211" s="46"/>
+      <c r="I211" s="77"/>
     </row>
     <row r="212" ht="13.5" customHeight="1">
-      <c r="A212" s="49"/>
-      <c r="I212" s="7"/>
-      <c r="J212" s="7"/>
+      <c r="A212" s="46"/>
+      <c r="I212" s="77"/>
     </row>
     <row r="213" ht="13.5" customHeight="1">
-      <c r="A213" s="49"/>
-      <c r="I213" s="7"/>
-      <c r="J213" s="7"/>
+      <c r="A213" s="46"/>
+      <c r="I213" s="77"/>
     </row>
     <row r="214" ht="13.5" customHeight="1">
-      <c r="A214" s="49"/>
-      <c r="I214" s="7"/>
-      <c r="J214" s="7"/>
+      <c r="A214" s="46"/>
+      <c r="I214" s="77"/>
     </row>
     <row r="215" ht="13.5" customHeight="1">
-      <c r="A215" s="49"/>
-      <c r="I215" s="7"/>
-      <c r="J215" s="7"/>
+      <c r="A215" s="46"/>
+      <c r="I215" s="77"/>
     </row>
     <row r="216" ht="13.5" customHeight="1">
-      <c r="A216" s="49"/>
-      <c r="I216" s="7"/>
-      <c r="J216" s="7"/>
+      <c r="A216" s="46"/>
+      <c r="I216" s="77"/>
     </row>
     <row r="217" ht="13.5" customHeight="1">
-      <c r="A217" s="49"/>
-      <c r="I217" s="7"/>
-      <c r="J217" s="7"/>
+      <c r="A217" s="46"/>
+      <c r="I217" s="77"/>
     </row>
     <row r="218" ht="13.5" customHeight="1">
-      <c r="A218" s="49"/>
-      <c r="I218" s="7"/>
-      <c r="J218" s="7"/>
+      <c r="A218" s="46"/>
+      <c r="I218" s="77"/>
     </row>
     <row r="219" ht="13.5" customHeight="1">
-      <c r="A219" s="49"/>
-      <c r="I219" s="7"/>
-      <c r="J219" s="7"/>
+      <c r="A219" s="46"/>
+      <c r="I219" s="77"/>
     </row>
     <row r="220" ht="13.5" customHeight="1">
-      <c r="A220" s="49"/>
-      <c r="I220" s="7"/>
-      <c r="J220" s="7"/>
+      <c r="A220" s="46"/>
+      <c r="I220" s="77"/>
     </row>
     <row r="221" ht="13.5" customHeight="1">
-      <c r="A221" s="49"/>
-      <c r="I221" s="7"/>
-      <c r="J221" s="7"/>
+      <c r="A221" s="46"/>
+      <c r="I221" s="77"/>
     </row>
     <row r="222" ht="13.5" customHeight="1">
-      <c r="A222" s="49"/>
-      <c r="I222" s="7"/>
-      <c r="J222" s="7"/>
+      <c r="A222" s="46"/>
+      <c r="I222" s="77"/>
     </row>
     <row r="223" ht="13.5" customHeight="1">
-      <c r="A223" s="49"/>
-      <c r="I223" s="7"/>
-      <c r="J223" s="7"/>
+      <c r="A223" s="46"/>
+      <c r="I223" s="77"/>
     </row>
     <row r="224" ht="13.5" customHeight="1">
-      <c r="A224" s="49"/>
-      <c r="I224" s="7"/>
-      <c r="J224" s="7"/>
+      <c r="A224" s="46"/>
+      <c r="I224" s="77"/>
     </row>
     <row r="225" ht="13.5" customHeight="1">
-      <c r="A225" s="49"/>
-      <c r="I225" s="7"/>
-      <c r="J225" s="7"/>
+      <c r="A225" s="46"/>
+      <c r="I225" s="77"/>
     </row>
     <row r="226" ht="13.5" customHeight="1">
-      <c r="A226" s="49"/>
-      <c r="I226" s="7"/>
-      <c r="J226" s="7"/>
+      <c r="A226" s="46"/>
+      <c r="I226" s="77"/>
     </row>
     <row r="227" ht="13.5" customHeight="1">
-      <c r="A227" s="49"/>
-      <c r="I227" s="7"/>
-      <c r="J227" s="7"/>
+      <c r="A227" s="46"/>
+      <c r="I227" s="77"/>
     </row>
     <row r="228" ht="13.5" customHeight="1">
-      <c r="A228" s="49"/>
-      <c r="I228" s="7"/>
-      <c r="J228" s="7"/>
+      <c r="A228" s="46"/>
+      <c r="I228" s="77"/>
     </row>
     <row r="229" ht="13.5" customHeight="1">
-      <c r="A229" s="49"/>
-      <c r="I229" s="7"/>
-      <c r="J229" s="7"/>
+      <c r="A229" s="46"/>
+      <c r="I229" s="77"/>
     </row>
     <row r="230" ht="13.5" customHeight="1">
-      <c r="A230" s="49"/>
-      <c r="I230" s="7"/>
-      <c r="J230" s="7"/>
+      <c r="A230" s="46"/>
+      <c r="I230" s="77"/>
     </row>
     <row r="231" ht="13.5" customHeight="1">
-      <c r="A231" s="49"/>
-      <c r="I231" s="7"/>
-      <c r="J231" s="7"/>
+      <c r="A231" s="46"/>
+      <c r="I231" s="77"/>
     </row>
     <row r="232" ht="13.5" customHeight="1">
-      <c r="A232" s="49"/>
-      <c r="I232" s="7"/>
-      <c r="J232" s="7"/>
+      <c r="A232" s="46"/>
+      <c r="I232" s="77"/>
     </row>
     <row r="233" ht="13.5" customHeight="1">
-      <c r="A233" s="49"/>
-      <c r="I233" s="7"/>
-      <c r="J233" s="7"/>
+      <c r="A233" s="46"/>
+      <c r="I233" s="77"/>
     </row>
     <row r="234" ht="13.5" customHeight="1">
-      <c r="A234" s="49"/>
-      <c r="I234" s="7"/>
-      <c r="J234" s="7"/>
+      <c r="A234" s="46"/>
+      <c r="I234" s="77"/>
     </row>
     <row r="235" ht="13.5" customHeight="1">
-      <c r="A235" s="49"/>
-      <c r="I235" s="7"/>
-      <c r="J235" s="7"/>
+      <c r="A235" s="46"/>
+      <c r="I235" s="77"/>
     </row>
     <row r="236" ht="13.5" customHeight="1">
-      <c r="A236" s="49"/>
-      <c r="I236" s="7"/>
-      <c r="J236" s="7"/>
+      <c r="A236" s="46"/>
+      <c r="I236" s="77"/>
     </row>
     <row r="237" ht="13.5" customHeight="1">
-      <c r="A237" s="49"/>
-      <c r="I237" s="7"/>
-      <c r="J237" s="7"/>
+      <c r="A237" s="46"/>
+      <c r="I237" s="77"/>
     </row>
     <row r="238" ht="13.5" customHeight="1">
-      <c r="A238" s="49"/>
-      <c r="I238" s="7"/>
-      <c r="J238" s="7"/>
+      <c r="A238" s="46"/>
+      <c r="I238" s="77"/>
     </row>
     <row r="239" ht="13.5" customHeight="1">
-      <c r="A239" s="49"/>
-      <c r="I239" s="7"/>
-      <c r="J239" s="7"/>
+      <c r="A239" s="46"/>
+      <c r="I239" s="77"/>
     </row>
     <row r="240" ht="13.5" customHeight="1">
-      <c r="A240" s="49"/>
-      <c r="I240" s="7"/>
-      <c r="J240" s="7"/>
+      <c r="A240" s="46"/>
+      <c r="I240" s="77"/>
     </row>
     <row r="241" ht="13.5" customHeight="1">
-      <c r="A241" s="49"/>
-      <c r="I241" s="7"/>
-      <c r="J241" s="7"/>
+      <c r="A241" s="46"/>
+      <c r="I241" s="77"/>
     </row>
     <row r="242" ht="13.5" customHeight="1">
-      <c r="A242" s="49"/>
-      <c r="I242" s="7"/>
-      <c r="J242" s="7"/>
+      <c r="A242" s="46"/>
+      <c r="I242" s="77"/>
     </row>
     <row r="243" ht="13.5" customHeight="1">
-      <c r="A243" s="49"/>
-      <c r="I243" s="7"/>
-      <c r="J243" s="7"/>
+      <c r="A243" s="46"/>
+      <c r="I243" s="77"/>
     </row>
     <row r="244" ht="13.5" customHeight="1">
-      <c r="A244" s="49"/>
-      <c r="I244" s="7"/>
-      <c r="J244" s="7"/>
+      <c r="A244" s="46"/>
+      <c r="I244" s="77"/>
     </row>
     <row r="245" ht="13.5" customHeight="1">
-      <c r="A245" s="49"/>
-      <c r="I245" s="7"/>
-      <c r="J245" s="7"/>
+      <c r="A245" s="46"/>
+      <c r="I245" s="77"/>
     </row>
     <row r="246" ht="13.5" customHeight="1">
-      <c r="A246" s="49"/>
-      <c r="I246" s="7"/>
-      <c r="J246" s="7"/>
+      <c r="A246" s="46"/>
+      <c r="I246" s="77"/>
     </row>
     <row r="247" ht="13.5" customHeight="1">
-      <c r="A247" s="49"/>
-      <c r="I247" s="7"/>
-      <c r="J247" s="7"/>
+      <c r="A247" s="46"/>
+      <c r="I247" s="77"/>
     </row>
     <row r="248" ht="13.5" customHeight="1">
-      <c r="A248" s="49"/>
-      <c r="I248" s="7"/>
-      <c r="J248" s="7"/>
+      <c r="A248" s="46"/>
+      <c r="I248" s="77"/>
     </row>
     <row r="249" ht="13.5" customHeight="1">
-      <c r="A249" s="49"/>
-      <c r="I249" s="7"/>
-      <c r="J249" s="7"/>
+      <c r="A249" s="46"/>
+      <c r="I249" s="77"/>
     </row>
     <row r="250" ht="13.5" customHeight="1">
-      <c r="A250" s="49"/>
-      <c r="I250" s="7"/>
-      <c r="J250" s="7"/>
+      <c r="A250" s="46"/>
+      <c r="I250" s="77"/>
     </row>
     <row r="251" ht="13.5" customHeight="1">
-      <c r="A251" s="49"/>
-      <c r="I251" s="7"/>
-      <c r="J251" s="7"/>
+      <c r="A251" s="46"/>
+      <c r="I251" s="77"/>
     </row>
     <row r="252" ht="13.5" customHeight="1">
-      <c r="A252" s="49"/>
-      <c r="I252" s="7"/>
-      <c r="J252" s="7"/>
+      <c r="A252" s="46"/>
+      <c r="I252" s="77"/>
     </row>
     <row r="253" ht="13.5" customHeight="1">
-      <c r="A253" s="49"/>
-      <c r="I253" s="7"/>
-      <c r="J253" s="7"/>
+      <c r="A253" s="46"/>
+      <c r="I253" s="77"/>
     </row>
     <row r="254" ht="13.5" customHeight="1">
-      <c r="A254" s="49"/>
-      <c r="I254" s="7"/>
-      <c r="J254" s="7"/>
+      <c r="A254" s="46"/>
+      <c r="I254" s="77"/>
     </row>
     <row r="255" ht="13.5" customHeight="1">
-      <c r="A255" s="49"/>
-      <c r="I255" s="7"/>
-      <c r="J255" s="7"/>
+      <c r="A255" s="46"/>
+      <c r="I255" s="77"/>
     </row>
     <row r="256" ht="13.5" customHeight="1">
-      <c r="A256" s="49"/>
-      <c r="I256" s="7"/>
-      <c r="J256" s="7"/>
+      <c r="A256" s="46"/>
+      <c r="I256" s="77"/>
     </row>
     <row r="257" ht="13.5" customHeight="1">
-      <c r="A257" s="49"/>
-      <c r="I257" s="7"/>
-      <c r="J257" s="7"/>
+      <c r="A257" s="46"/>
+      <c r="I257" s="77"/>
     </row>
     <row r="258" ht="13.5" customHeight="1">
-      <c r="A258" s="49"/>
-      <c r="I258" s="7"/>
-      <c r="J258" s="7"/>
+      <c r="A258" s="46"/>
+      <c r="I258" s="77"/>
     </row>
     <row r="259" ht="13.5" customHeight="1">
-      <c r="A259" s="49"/>
-      <c r="I259" s="7"/>
-      <c r="J259" s="7"/>
+      <c r="A259" s="46"/>
+      <c r="I259" s="77"/>
     </row>
     <row r="260" ht="13.5" customHeight="1">
-      <c r="A260" s="49"/>
-      <c r="I260" s="7"/>
-      <c r="J260" s="7"/>
+      <c r="A260" s="46"/>
+      <c r="I260" s="77"/>
     </row>
     <row r="261" ht="13.5" customHeight="1">
-      <c r="A261" s="49"/>
-      <c r="I261" s="7"/>
-      <c r="J261" s="7"/>
+      <c r="A261" s="46"/>
+      <c r="I261" s="77"/>
     </row>
     <row r="262" ht="13.5" customHeight="1">
-      <c r="A262" s="49"/>
-      <c r="I262" s="7"/>
-      <c r="J262" s="7"/>
+      <c r="A262" s="46"/>
+      <c r="I262" s="77"/>
     </row>
     <row r="263" ht="13.5" customHeight="1">
-      <c r="A263" s="49"/>
-      <c r="I263" s="7"/>
-      <c r="J263" s="7"/>
+      <c r="A263" s="46"/>
+      <c r="I263" s="77"/>
     </row>
     <row r="264" ht="13.5" customHeight="1">
-      <c r="A264" s="49"/>
-      <c r="I264" s="7"/>
-      <c r="J264" s="7"/>
+      <c r="A264" s="46"/>
+      <c r="I264" s="77"/>
     </row>
     <row r="265" ht="13.5" customHeight="1">
-      <c r="A265" s="49"/>
-      <c r="I265" s="7"/>
-      <c r="J265" s="7"/>
+      <c r="A265" s="46"/>
+      <c r="I265" s="77"/>
     </row>
     <row r="266" ht="13.5" customHeight="1">
-      <c r="A266" s="49"/>
-      <c r="I266" s="7"/>
-      <c r="J266" s="7"/>
+      <c r="A266" s="46"/>
+      <c r="I266" s="77"/>
     </row>
     <row r="267" ht="13.5" customHeight="1">
-      <c r="A267" s="49"/>
-      <c r="I267" s="7"/>
-      <c r="J267" s="7"/>
+      <c r="A267" s="46"/>
+      <c r="I267" s="77"/>
     </row>
     <row r="268" ht="13.5" customHeight="1">
-      <c r="A268" s="49"/>
-      <c r="I268" s="7"/>
-      <c r="J268" s="7"/>
+      <c r="A268" s="46"/>
+      <c r="I268" s="77"/>
     </row>
     <row r="269" ht="13.5" customHeight="1">
-      <c r="A269" s="49"/>
-      <c r="I269" s="7"/>
-      <c r="J269" s="7"/>
+      <c r="A269" s="46"/>
+      <c r="I269" s="77"/>
     </row>
     <row r="270" ht="13.5" customHeight="1">
-      <c r="A270" s="49"/>
-      <c r="I270" s="7"/>
-      <c r="J270" s="7"/>
+      <c r="A270" s="46"/>
+      <c r="I270" s="77"/>
     </row>
     <row r="271" ht="13.5" customHeight="1">
-      <c r="A271" s="49"/>
+      <c r="A271" s="46"/>
     </row>
     <row r="272" ht="13.5" customHeight="1"/>
     <row r="273" ht="13.5" customHeight="1"/>
@@ -3187,7 +2906,7 @@
     <row r="729" ht="13.5" customHeight="1"/>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{F449C9FB-110E-4907-A94A-54D72BF9B0FC}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{B11FEEE2-625F-4AAF-8B49-E70FE5F66624}" filter="1" showAutoFilter="1">
       <autoFilter ref="$I$1:$I$563"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
@@ -3195,7 +2914,7 @@
         </ext>
       </extLst>
     </customSheetView>
-    <customSheetView guid="{3A8DA5CB-6C4D-47B2-A680-E0971AEA3492}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{E030274F-D8A4-4B1C-84F1-2CAF425A2CE5}" filter="1" showAutoFilter="1">
       <autoFilter ref="$I$1:$I$563"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">

--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -44,8 +44,8 @@
     <definedName name="Templates">#REF!</definedName>
     <definedName name="hronSEC">#REF!</definedName>
     <definedName localSheetId="0" name="SMETA_TITLE">EXPORT_TMP!$B$7</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_B11FEEE2_625F_4AAF_8B49_E70FE5F66624_.wvu.FilterData">EXPORT_TMP!$I$1:$I$563</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_E030274F_D8A4_4B1C_84F1_2CAF425A2CE5_.wvu.FilterData">EXPORT_TMP!$I$1:$I$563</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_8DF02645_97DB_4BA1_8860_6E858A7D8324_.wvu.FilterData">EXPORT_TMP!$I$1:$I$563</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_4642DB06_625C_40F7_B187_56563CB26E82_.wvu.FilterData">EXPORT_TMP!$I$1:$I$563</definedName>
     <definedName name="CLIENT_PRICE">LAMBDA(себестоимость, вашмаркап, налог, округление, IFERROR(ROUNDUP(себестоимость*(1+вашмаркап/100)/(1-1*налог),округление),0))</definedName>
     <definedName name="CONDUCT_CALC">LAMBDA(стоимость, количество, налог, IFERROR(PRODUCT(количество, стоимость) / TAX_CONVERTER(налог), 0))</definedName>
     <definedName name="MARKET_FEE">LAMBDA(процент, сумма_до_налога, MIN(сумма_до_налога, 2000000) * процент + MAX(0, сумма_до_налога - 2000000) * (процент / 2))</definedName>
@@ -53,8 +53,8 @@
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{B11FEEE2-625F-4AAF-8B49-E70FE5F66624}" name="nozero"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{E030274F-D8A4-4B1C-84F1-2CAF425A2CE5}" name="WithZeros"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{4642DB06-625C-40F7-B187-56563CB26E82}" name="nozero"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{8DF02645-97DB-4BA1-8860-6E858A7D8324}" name="WithZeros"/>
   </customWorkbookViews>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -198,7 +198,7 @@
     <numFmt numFmtId="164" formatCode="\+#\ \(###\)\ ###\-##\-##"/>
     <numFmt numFmtId="165" formatCode="[$-FC19]dd\ mmmm\ yyyy\ \г\."/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -218,11 +218,6 @@
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Montserrat"/>
-    </font>
-    <font>
-      <sz val="8.0"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Montserrat"/>
     </font>
     <font>
@@ -609,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="74">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -624,11 +619,10 @@
     </xf>
     <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -640,8 +634,7 @@
     <xf borderId="7" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -650,166 +643,162 @@
     </xf>
     <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="13" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="2" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="13" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="14" fillId="2" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="15" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="2" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="15" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="14" fillId="2" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="17" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="17" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="18" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="19" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="19" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="20" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="20" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="21" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="22" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="21" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="22" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf borderId="2" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="23" fillId="3" fontId="14" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf borderId="17" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf borderId="19" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf borderId="10" fillId="3" fontId="14" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="14" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="14" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="16" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="top"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="11" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf borderId="3" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf borderId="14" fillId="3" fontId="15" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="23" fillId="3" fontId="15" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="2" fontId="13" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf borderId="17" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf borderId="19" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf borderId="10" fillId="3" fontId="15" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="15" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="15" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="17" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="12" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="24" fillId="3" fontId="15" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="25" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="26" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="11" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf borderId="23" fillId="3" fontId="14" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="14" fillId="2" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="3" fontId="16" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="3" fontId="14" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="17" fillId="2" fontId="19" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="18" fillId="2" fontId="20" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="14" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="18" fillId="2" fontId="19" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="24" fillId="3" fontId="16" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="19" fillId="2" fontId="19" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf borderId="14" fillId="2" fontId="11" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="25" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="26" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="12" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf borderId="23" fillId="3" fontId="15" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="2" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="15" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="17" fillId="2" fontId="20" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="18" fillId="2" fontId="21" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf borderId="18" fillId="2" fontId="20" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf borderId="19" fillId="2" fontId="20" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf borderId="14" fillId="2" fontId="12" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="14" fillId="2" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="14" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="14" fillId="2" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="14" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="14" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="27" fillId="0" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="27" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="27" fillId="0" fontId="24" numFmtId="3" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="27" fillId="0" fontId="24" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="27" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="27" fillId="0" fontId="23" numFmtId="3" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="27" fillId="0" fontId="23" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="27" fillId="0" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="28" fillId="3" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="28" fillId="3" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="28" fillId="3" fontId="26" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="28" fillId="3" fontId="25" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="28" fillId="3" fontId="26" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="28" fillId="3" fontId="25" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1059,1392 +1048,1310 @@
       <c r="F1" s="4"/>
       <c r="G1" s="5"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="6"/>
     </row>
     <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8" t="e">
+      <c r="A2" s="6"/>
+      <c r="B2" s="7" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="11" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="12"/>
     </row>
     <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="7"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="11" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="12"/>
     </row>
     <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="10"/>
     </row>
     <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="7"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="19">
+      <c r="A5" s="6"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="17">
         <v>7.4951331645E10</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="21" t="s">
+      <c r="D5" s="18"/>
+      <c r="E5" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="22"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="23" t="s">
+      <c r="F5" s="20"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="12"/>
     </row>
     <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="7"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="12"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="24"/>
     </row>
     <row r="7" ht="28.5" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="27" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="12"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" ht="13.5" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="30" t="s">
+      <c r="A8" s="6"/>
+      <c r="B8" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="12"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="34" t="s">
+      <c r="A9" s="6"/>
+      <c r="B9" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="33">
         <v>1.0</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="38" t="s">
+      <c r="D9" s="34"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="39">
+      <c r="G9" s="37">
         <v>30.0</v>
       </c>
-      <c r="H9" s="40" t="s">
+      <c r="H9" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="12"/>
     </row>
     <row r="10" ht="13.5" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="45"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="42"/>
     </row>
     <row r="11" ht="13.5" customHeight="1">
-      <c r="A11" s="46"/>
-      <c r="B11" s="34" t="s">
+      <c r="A11" s="43"/>
+      <c r="B11" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="33">
         <v>0.0</v>
       </c>
-      <c r="D11" s="40"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="38" t="s">
+      <c r="D11" s="38"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="39">
+      <c r="G11" s="37">
         <v>30.0</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="H11" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="12"/>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="12"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="46"/>
     </row>
     <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="50"/>
-      <c r="B13" s="34" t="s">
+      <c r="A13" s="47"/>
+      <c r="B13" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="51" t="s">
+      <c r="C13" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="12"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="50"/>
-      <c r="B14" s="52"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="12"/>
+      <c r="A14" s="47"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="46"/>
     </row>
     <row r="15" ht="13.5" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="34" t="s">
+      <c r="A15" s="6"/>
+      <c r="B15" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="C15" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="56"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="12"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="54"/>
     </row>
     <row r="16" ht="13.5" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="52"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="12"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
     </row>
     <row r="17" ht="13.5" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="34" t="s">
+      <c r="A17" s="6"/>
+      <c r="B17" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="55" t="s">
+      <c r="C17" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="12"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="54"/>
     </row>
     <row r="18" ht="13.5" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="12"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="55"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="55"/>
     </row>
     <row r="19" ht="13.5" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="34" t="s">
+      <c r="A19" s="6"/>
+      <c r="B19" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="59">
+      <c r="C19" s="56">
         <v>1.0</v>
       </c>
-      <c r="D19" s="60" t="s">
+      <c r="D19" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="61">
+      <c r="E19" s="20"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="58">
         <v>10.0</v>
       </c>
-      <c r="H19" s="40" t="s">
+      <c r="H19" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="I19" s="12"/>
     </row>
     <row r="20" ht="13.5" customHeight="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="62"/>
-      <c r="C20" s="63" t="s">
+      <c r="A20" s="6"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64"/>
-      <c r="F20" s="64"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="65"/>
-      <c r="I20" s="12"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="62"/>
     </row>
     <row r="21" ht="13.5" customHeight="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="34" t="s">
+      <c r="A21" s="6"/>
+      <c r="B21" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="66">
+      <c r="C21" s="63">
         <v>45809.654539027775</v>
       </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="67" t="s">
+      <c r="D21" s="18"/>
+      <c r="E21" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="12"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="18"/>
     </row>
     <row r="22" ht="13.5" customHeight="1">
-      <c r="A22" s="46"/>
-      <c r="B22" s="34" t="s">
+      <c r="A22" s="43"/>
+      <c r="B22" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="45"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="18"/>
     </row>
     <row r="23" ht="13.5" customHeight="1">
-      <c r="A23" s="46"/>
-      <c r="B23" s="34" t="s">
+      <c r="A23" s="43"/>
+      <c r="B23" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="68" t="s">
+      <c r="C23" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="45"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="18"/>
     </row>
     <row r="24" ht="13.5" customHeight="1">
-      <c r="A24" s="46"/>
-      <c r="B24" s="34"/>
-      <c r="C24" s="68" t="s">
+      <c r="A24" s="43"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="45"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="18"/>
     </row>
     <row r="25" ht="13.5" customHeight="1">
-      <c r="A25" s="46"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="68" t="s">
+      <c r="A25" s="43"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="45"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="18"/>
     </row>
     <row r="26" ht="13.5" customHeight="1">
-      <c r="A26" s="46"/>
-      <c r="B26" s="34" t="s">
+      <c r="A26" s="43"/>
+      <c r="B26" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="68" t="s">
+      <c r="C26" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="45"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="18"/>
     </row>
     <row r="27" ht="63.75" customHeight="1">
-      <c r="A27" s="46"/>
-      <c r="B27" s="34" t="s">
+      <c r="A27" s="43"/>
+      <c r="B27" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="69" t="s">
+      <c r="C27" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="12"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="18"/>
     </row>
     <row r="28" ht="13.5" customHeight="1">
-      <c r="A28" s="46"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="12"/>
+      <c r="A28" s="43"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="18"/>
     </row>
     <row r="29" ht="13.5" customHeight="1">
-      <c r="A29" s="7"/>
-      <c r="B29" s="70" t="s">
+      <c r="A29" s="6"/>
+      <c r="B29" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="71"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="72"/>
-      <c r="F29" s="72"/>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73" t="s">
+      <c r="C29" s="68"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="I29" s="12"/>
     </row>
     <row r="30" ht="13.5" customHeight="1">
-      <c r="A30" s="46"/>
-      <c r="B30" s="74" t="s">
+      <c r="A30" s="43"/>
+      <c r="B30" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="75" t="s">
+      <c r="C30" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="74" t="s">
+      <c r="D30" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="74" t="s">
+      <c r="E30" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="74" t="s">
+      <c r="F30" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="G30" s="74" t="s">
+      <c r="G30" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="H30" s="76" t="s">
+      <c r="H30" s="73" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="46"/>
-      <c r="I31" s="77"/>
+      <c r="A31" s="43"/>
+      <c r="I31" s="43"/>
     </row>
     <row r="32" ht="13.5" customHeight="1">
-      <c r="A32" s="46"/>
-      <c r="I32" s="77"/>
+      <c r="A32" s="43"/>
+      <c r="I32" s="43"/>
     </row>
     <row r="33" ht="13.5" customHeight="1">
-      <c r="A33" s="46"/>
-      <c r="I33" s="77"/>
+      <c r="A33" s="43"/>
+      <c r="I33" s="43"/>
     </row>
     <row r="34" ht="13.5" customHeight="1">
-      <c r="A34" s="46"/>
-      <c r="I34" s="77"/>
+      <c r="A34" s="43"/>
+      <c r="I34" s="43"/>
     </row>
     <row r="35" ht="13.5" customHeight="1">
-      <c r="A35" s="46"/>
-      <c r="I35" s="77"/>
+      <c r="A35" s="43"/>
+      <c r="I35" s="43"/>
     </row>
     <row r="36" ht="13.5" customHeight="1">
-      <c r="A36" s="46"/>
-      <c r="I36" s="77"/>
+      <c r="A36" s="43"/>
+      <c r="I36" s="43"/>
     </row>
     <row r="37" ht="13.5" customHeight="1">
-      <c r="A37" s="46"/>
-      <c r="I37" s="77"/>
+      <c r="A37" s="43"/>
+      <c r="I37" s="43"/>
     </row>
     <row r="38" ht="13.5" customHeight="1">
-      <c r="A38" s="46"/>
-      <c r="I38" s="77"/>
+      <c r="A38" s="43"/>
+      <c r="I38" s="43"/>
     </row>
     <row r="39" ht="13.5" customHeight="1">
-      <c r="A39" s="46"/>
-      <c r="I39" s="77"/>
+      <c r="A39" s="43"/>
+      <c r="I39" s="43"/>
     </row>
     <row r="40" ht="13.5" customHeight="1">
-      <c r="A40" s="46"/>
-      <c r="I40" s="77"/>
+      <c r="A40" s="43"/>
+      <c r="I40" s="43"/>
     </row>
     <row r="41" ht="13.5" customHeight="1">
-      <c r="A41" s="46"/>
-      <c r="I41" s="77"/>
+      <c r="A41" s="43"/>
+      <c r="I41" s="43"/>
     </row>
     <row r="42" ht="13.5" customHeight="1">
-      <c r="A42" s="46"/>
-      <c r="I42" s="77"/>
+      <c r="A42" s="43"/>
+      <c r="I42" s="43"/>
     </row>
     <row r="43" ht="13.5" customHeight="1">
-      <c r="A43" s="46"/>
-      <c r="I43" s="77"/>
+      <c r="A43" s="43"/>
+      <c r="I43" s="43"/>
     </row>
     <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="46"/>
-      <c r="I44" s="77"/>
+      <c r="A44" s="43"/>
+      <c r="I44" s="43"/>
     </row>
     <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="46"/>
-      <c r="I45" s="77"/>
+      <c r="A45" s="43"/>
+      <c r="I45" s="43"/>
     </row>
     <row r="46" ht="13.5" customHeight="1">
-      <c r="A46" s="46"/>
-      <c r="I46" s="77"/>
+      <c r="A46" s="43"/>
+      <c r="I46" s="43"/>
     </row>
     <row r="47" ht="13.5" customHeight="1">
-      <c r="A47" s="46"/>
-      <c r="I47" s="77"/>
+      <c r="A47" s="43"/>
+      <c r="I47" s="43"/>
     </row>
     <row r="48" ht="13.5" customHeight="1">
-      <c r="A48" s="46"/>
-      <c r="I48" s="77"/>
+      <c r="A48" s="43"/>
+      <c r="I48" s="43"/>
     </row>
     <row r="49" ht="13.5" customHeight="1">
-      <c r="A49" s="46"/>
-      <c r="I49" s="77"/>
+      <c r="A49" s="43"/>
+      <c r="I49" s="43"/>
     </row>
     <row r="50" ht="13.5" customHeight="1">
-      <c r="A50" s="46"/>
-      <c r="I50" s="77"/>
+      <c r="A50" s="43"/>
+      <c r="I50" s="43"/>
     </row>
     <row r="51" ht="13.5" customHeight="1">
-      <c r="A51" s="46"/>
-      <c r="I51" s="77"/>
+      <c r="A51" s="43"/>
+      <c r="I51" s="43"/>
     </row>
     <row r="52" ht="13.5" customHeight="1">
-      <c r="A52" s="46"/>
-      <c r="I52" s="77"/>
+      <c r="A52" s="43"/>
+      <c r="I52" s="43"/>
     </row>
     <row r="53" ht="13.5" customHeight="1">
-      <c r="A53" s="46"/>
-      <c r="I53" s="77"/>
+      <c r="A53" s="43"/>
+      <c r="I53" s="43"/>
     </row>
     <row r="54" ht="13.5" customHeight="1">
-      <c r="A54" s="46"/>
-      <c r="I54" s="77"/>
+      <c r="A54" s="43"/>
+      <c r="I54" s="43"/>
     </row>
     <row r="55" ht="13.5" customHeight="1">
-      <c r="A55" s="46"/>
-      <c r="I55" s="77"/>
+      <c r="A55" s="43"/>
+      <c r="I55" s="43"/>
     </row>
     <row r="56" ht="13.5" customHeight="1">
-      <c r="A56" s="46"/>
-      <c r="I56" s="77"/>
+      <c r="A56" s="43"/>
+      <c r="I56" s="43"/>
     </row>
     <row r="57" ht="13.5" customHeight="1">
-      <c r="A57" s="46"/>
-      <c r="I57" s="77"/>
+      <c r="A57" s="43"/>
+      <c r="I57" s="43"/>
     </row>
     <row r="58" ht="13.5" customHeight="1">
-      <c r="A58" s="46"/>
-      <c r="I58" s="77"/>
+      <c r="A58" s="43"/>
+      <c r="I58" s="43"/>
     </row>
     <row r="59" ht="13.5" customHeight="1">
-      <c r="A59" s="46"/>
-      <c r="I59" s="77"/>
+      <c r="A59" s="43"/>
+      <c r="I59" s="43"/>
     </row>
     <row r="60" ht="13.5" customHeight="1">
-      <c r="A60" s="46"/>
-      <c r="I60" s="77"/>
+      <c r="A60" s="43"/>
+      <c r="I60" s="43"/>
     </row>
     <row r="61" ht="13.5" customHeight="1">
-      <c r="A61" s="46"/>
-      <c r="I61" s="77"/>
+      <c r="A61" s="43"/>
+      <c r="I61" s="43"/>
     </row>
     <row r="62" ht="13.5" customHeight="1">
-      <c r="A62" s="46"/>
-      <c r="I62" s="77"/>
+      <c r="A62" s="43"/>
+      <c r="I62" s="43"/>
     </row>
     <row r="63" ht="13.5" customHeight="1">
-      <c r="A63" s="46"/>
-      <c r="I63" s="77"/>
+      <c r="A63" s="43"/>
+      <c r="I63" s="43"/>
     </row>
     <row r="64" ht="13.5" customHeight="1">
-      <c r="A64" s="46"/>
-      <c r="I64" s="77"/>
+      <c r="A64" s="43"/>
+      <c r="I64" s="43"/>
     </row>
     <row r="65" ht="13.5" customHeight="1">
-      <c r="A65" s="46"/>
-      <c r="I65" s="77"/>
+      <c r="A65" s="43"/>
+      <c r="I65" s="43"/>
     </row>
     <row r="66" ht="13.5" customHeight="1">
-      <c r="A66" s="46"/>
-      <c r="I66" s="77"/>
+      <c r="A66" s="43"/>
+      <c r="I66" s="43"/>
     </row>
     <row r="67" ht="13.5" customHeight="1">
-      <c r="A67" s="46"/>
-      <c r="I67" s="77"/>
+      <c r="A67" s="43"/>
+      <c r="I67" s="43"/>
     </row>
     <row r="68" ht="13.5" customHeight="1">
-      <c r="A68" s="46"/>
-      <c r="I68" s="77"/>
+      <c r="A68" s="43"/>
+      <c r="I68" s="43"/>
     </row>
     <row r="69" ht="13.5" customHeight="1">
-      <c r="A69" s="46"/>
-      <c r="I69" s="77"/>
+      <c r="A69" s="43"/>
+      <c r="I69" s="43"/>
     </row>
     <row r="70" ht="13.5" customHeight="1">
-      <c r="A70" s="46"/>
-      <c r="I70" s="77"/>
+      <c r="A70" s="43"/>
+      <c r="I70" s="43"/>
     </row>
     <row r="71" ht="13.5" customHeight="1">
-      <c r="A71" s="46"/>
-      <c r="I71" s="77"/>
+      <c r="A71" s="43"/>
+      <c r="I71" s="43"/>
     </row>
     <row r="72" ht="13.5" customHeight="1">
-      <c r="A72" s="46"/>
-      <c r="I72" s="77"/>
+      <c r="A72" s="43"/>
+      <c r="I72" s="43"/>
     </row>
     <row r="73" ht="13.5" customHeight="1">
-      <c r="A73" s="46"/>
-      <c r="I73" s="77"/>
+      <c r="A73" s="43"/>
+      <c r="I73" s="43"/>
     </row>
     <row r="74" ht="13.5" customHeight="1">
-      <c r="A74" s="46"/>
-      <c r="I74" s="77"/>
+      <c r="A74" s="43"/>
+      <c r="I74" s="43"/>
     </row>
     <row r="75" ht="13.5" customHeight="1">
-      <c r="A75" s="46"/>
-      <c r="I75" s="77"/>
+      <c r="A75" s="43"/>
+      <c r="I75" s="43"/>
     </row>
     <row r="76" ht="13.5" customHeight="1">
-      <c r="A76" s="46"/>
-      <c r="I76" s="77"/>
+      <c r="A76" s="43"/>
+      <c r="I76" s="43"/>
     </row>
     <row r="77" ht="13.5" customHeight="1">
-      <c r="A77" s="46"/>
-      <c r="I77" s="77"/>
+      <c r="A77" s="43"/>
+      <c r="I77" s="43"/>
     </row>
     <row r="78" ht="13.5" customHeight="1">
-      <c r="A78" s="46"/>
-      <c r="I78" s="77"/>
+      <c r="A78" s="43"/>
+      <c r="I78" s="43"/>
     </row>
     <row r="79" ht="13.5" customHeight="1">
-      <c r="A79" s="46"/>
-      <c r="I79" s="77"/>
+      <c r="A79" s="43"/>
+      <c r="I79" s="43"/>
     </row>
     <row r="80" ht="13.5" customHeight="1">
-      <c r="A80" s="46"/>
-      <c r="I80" s="77"/>
+      <c r="A80" s="43"/>
+      <c r="I80" s="43"/>
     </row>
     <row r="81" ht="13.5" customHeight="1">
-      <c r="A81" s="46"/>
-      <c r="I81" s="77"/>
+      <c r="A81" s="43"/>
+      <c r="I81" s="43"/>
     </row>
     <row r="82" ht="13.5" customHeight="1">
-      <c r="A82" s="46"/>
-      <c r="I82" s="77"/>
+      <c r="A82" s="43"/>
+      <c r="I82" s="43"/>
     </row>
     <row r="83" ht="13.5" customHeight="1">
-      <c r="A83" s="46"/>
-      <c r="I83" s="77"/>
+      <c r="A83" s="43"/>
+      <c r="I83" s="43"/>
     </row>
     <row r="84" ht="13.5" customHeight="1">
-      <c r="A84" s="46"/>
-      <c r="I84" s="77"/>
+      <c r="A84" s="43"/>
+      <c r="I84" s="43"/>
     </row>
     <row r="85" ht="13.5" customHeight="1">
-      <c r="A85" s="46"/>
-      <c r="I85" s="77"/>
+      <c r="A85" s="43"/>
+      <c r="I85" s="43"/>
     </row>
     <row r="86" ht="13.5" customHeight="1">
-      <c r="A86" s="46"/>
-      <c r="I86" s="77"/>
+      <c r="A86" s="43"/>
+      <c r="I86" s="43"/>
     </row>
     <row r="87" ht="13.5" customHeight="1">
-      <c r="A87" s="46"/>
-      <c r="I87" s="77"/>
+      <c r="A87" s="43"/>
+      <c r="I87" s="43"/>
     </row>
     <row r="88" ht="13.5" customHeight="1">
-      <c r="A88" s="46"/>
-      <c r="I88" s="77"/>
+      <c r="A88" s="43"/>
+      <c r="I88" s="43"/>
     </row>
     <row r="89" ht="13.5" customHeight="1">
-      <c r="A89" s="46"/>
-      <c r="I89" s="77"/>
+      <c r="A89" s="43"/>
+      <c r="I89" s="43"/>
     </row>
     <row r="90" ht="13.5" customHeight="1">
-      <c r="A90" s="46"/>
-      <c r="I90" s="77"/>
+      <c r="A90" s="43"/>
+      <c r="I90" s="43"/>
     </row>
     <row r="91" ht="13.5" customHeight="1">
-      <c r="A91" s="46"/>
-      <c r="I91" s="77"/>
+      <c r="A91" s="43"/>
+      <c r="I91" s="43"/>
     </row>
     <row r="92" ht="13.5" customHeight="1">
-      <c r="A92" s="46"/>
-      <c r="I92" s="77"/>
+      <c r="A92" s="43"/>
+      <c r="I92" s="43"/>
     </row>
     <row r="93" ht="13.5" customHeight="1">
-      <c r="A93" s="46"/>
-      <c r="I93" s="77"/>
+      <c r="A93" s="43"/>
+      <c r="I93" s="43"/>
     </row>
     <row r="94" ht="13.5" customHeight="1">
-      <c r="A94" s="46"/>
-      <c r="I94" s="77"/>
+      <c r="A94" s="43"/>
+      <c r="I94" s="43"/>
     </row>
     <row r="95" ht="13.5" customHeight="1">
-      <c r="A95" s="46"/>
-      <c r="I95" s="77"/>
+      <c r="A95" s="43"/>
+      <c r="I95" s="43"/>
     </row>
     <row r="96" ht="13.5" customHeight="1">
-      <c r="A96" s="46"/>
-      <c r="I96" s="77"/>
+      <c r="A96" s="43"/>
+      <c r="I96" s="43"/>
     </row>
     <row r="97" ht="13.5" customHeight="1">
-      <c r="A97" s="46"/>
-      <c r="I97" s="77"/>
+      <c r="A97" s="43"/>
+      <c r="I97" s="43"/>
     </row>
     <row r="98" ht="13.5" customHeight="1">
-      <c r="A98" s="46"/>
-      <c r="I98" s="77"/>
+      <c r="A98" s="43"/>
+      <c r="I98" s="43"/>
     </row>
     <row r="99" ht="13.5" customHeight="1">
-      <c r="A99" s="46"/>
-      <c r="I99" s="77"/>
+      <c r="A99" s="43"/>
+      <c r="I99" s="43"/>
     </row>
     <row r="100" ht="13.5" customHeight="1">
-      <c r="A100" s="46"/>
-      <c r="I100" s="77"/>
+      <c r="A100" s="43"/>
+      <c r="I100" s="43"/>
     </row>
     <row r="101" ht="13.5" customHeight="1">
-      <c r="A101" s="46"/>
-      <c r="I101" s="77"/>
+      <c r="A101" s="43"/>
+      <c r="I101" s="43"/>
     </row>
     <row r="102" ht="13.5" customHeight="1">
-      <c r="A102" s="46"/>
-      <c r="I102" s="77"/>
+      <c r="A102" s="43"/>
+      <c r="I102" s="43"/>
     </row>
     <row r="103" ht="13.5" customHeight="1">
-      <c r="A103" s="46"/>
-      <c r="I103" s="77"/>
+      <c r="A103" s="43"/>
+      <c r="I103" s="43"/>
     </row>
     <row r="104" ht="13.5" customHeight="1">
-      <c r="A104" s="46"/>
-      <c r="I104" s="77"/>
+      <c r="A104" s="43"/>
+      <c r="I104" s="43"/>
     </row>
     <row r="105" ht="13.5" customHeight="1">
-      <c r="A105" s="46"/>
-      <c r="I105" s="77"/>
+      <c r="A105" s="43"/>
+      <c r="I105" s="43"/>
     </row>
     <row r="106" ht="13.5" customHeight="1">
-      <c r="A106" s="46"/>
-      <c r="I106" s="77"/>
+      <c r="A106" s="43"/>
+      <c r="I106" s="43"/>
     </row>
     <row r="107" ht="13.5" customHeight="1">
-      <c r="A107" s="46"/>
-      <c r="I107" s="77"/>
+      <c r="A107" s="43"/>
+      <c r="I107" s="43"/>
     </row>
     <row r="108" ht="13.5" customHeight="1">
-      <c r="A108" s="46"/>
-      <c r="I108" s="77"/>
+      <c r="A108" s="43"/>
+      <c r="I108" s="43"/>
     </row>
     <row r="109" ht="13.5" customHeight="1">
-      <c r="A109" s="46"/>
-      <c r="I109" s="77"/>
+      <c r="A109" s="43"/>
+      <c r="I109" s="43"/>
     </row>
     <row r="110" ht="13.5" customHeight="1">
-      <c r="A110" s="46"/>
-      <c r="I110" s="77"/>
+      <c r="A110" s="43"/>
+      <c r="I110" s="43"/>
     </row>
     <row r="111" ht="13.5" customHeight="1">
-      <c r="A111" s="46"/>
-      <c r="I111" s="77"/>
+      <c r="A111" s="43"/>
+      <c r="I111" s="43"/>
     </row>
     <row r="112" ht="13.5" customHeight="1">
-      <c r="A112" s="46"/>
-      <c r="I112" s="77"/>
+      <c r="A112" s="43"/>
+      <c r="I112" s="43"/>
     </row>
     <row r="113" ht="13.5" customHeight="1">
-      <c r="A113" s="46"/>
-      <c r="I113" s="77"/>
+      <c r="A113" s="43"/>
+      <c r="I113" s="43"/>
     </row>
     <row r="114" ht="13.5" customHeight="1">
-      <c r="A114" s="46"/>
-      <c r="I114" s="77"/>
+      <c r="A114" s="43"/>
+      <c r="I114" s="43"/>
     </row>
     <row r="115" ht="13.5" customHeight="1">
-      <c r="A115" s="46"/>
-      <c r="I115" s="77"/>
+      <c r="A115" s="43"/>
+      <c r="I115" s="43"/>
     </row>
     <row r="116" ht="13.5" customHeight="1">
-      <c r="A116" s="46"/>
-      <c r="I116" s="77"/>
+      <c r="A116" s="43"/>
+      <c r="I116" s="43"/>
     </row>
     <row r="117" ht="13.5" customHeight="1">
-      <c r="A117" s="46"/>
-      <c r="I117" s="77"/>
+      <c r="A117" s="43"/>
+      <c r="I117" s="43"/>
     </row>
     <row r="118" ht="13.5" customHeight="1">
-      <c r="A118" s="46"/>
-      <c r="I118" s="77"/>
+      <c r="A118" s="43"/>
+      <c r="I118" s="43"/>
     </row>
     <row r="119" ht="13.5" customHeight="1">
-      <c r="A119" s="46"/>
-      <c r="I119" s="77"/>
+      <c r="A119" s="43"/>
+      <c r="I119" s="43"/>
     </row>
     <row r="120" ht="13.5" customHeight="1">
-      <c r="A120" s="46"/>
-      <c r="I120" s="77"/>
+      <c r="A120" s="43"/>
+      <c r="I120" s="43"/>
     </row>
     <row r="121" ht="13.5" customHeight="1">
-      <c r="A121" s="46"/>
-      <c r="I121" s="77"/>
+      <c r="A121" s="43"/>
+      <c r="I121" s="43"/>
     </row>
     <row r="122" ht="13.5" customHeight="1">
-      <c r="A122" s="46"/>
-      <c r="I122" s="77"/>
+      <c r="A122" s="43"/>
+      <c r="I122" s="43"/>
     </row>
     <row r="123" ht="13.5" customHeight="1">
-      <c r="A123" s="46"/>
-      <c r="I123" s="77"/>
+      <c r="A123" s="43"/>
+      <c r="I123" s="43"/>
     </row>
     <row r="124" ht="13.5" customHeight="1">
-      <c r="A124" s="46"/>
-      <c r="I124" s="77"/>
+      <c r="A124" s="43"/>
+      <c r="I124" s="43"/>
     </row>
     <row r="125" ht="13.5" customHeight="1">
-      <c r="A125" s="46"/>
-      <c r="I125" s="77"/>
+      <c r="A125" s="43"/>
+      <c r="I125" s="43"/>
     </row>
     <row r="126" ht="13.5" customHeight="1">
-      <c r="A126" s="46"/>
-      <c r="I126" s="77"/>
+      <c r="A126" s="43"/>
+      <c r="I126" s="43"/>
     </row>
     <row r="127" ht="13.5" customHeight="1">
-      <c r="A127" s="46"/>
-      <c r="I127" s="77"/>
+      <c r="A127" s="43"/>
+      <c r="I127" s="43"/>
     </row>
     <row r="128" ht="13.5" customHeight="1">
-      <c r="A128" s="46"/>
-      <c r="I128" s="77"/>
+      <c r="A128" s="43"/>
+      <c r="I128" s="43"/>
     </row>
     <row r="129" ht="13.5" customHeight="1">
-      <c r="A129" s="46"/>
-      <c r="I129" s="77"/>
+      <c r="A129" s="43"/>
+      <c r="I129" s="43"/>
     </row>
     <row r="130" ht="13.5" customHeight="1">
-      <c r="A130" s="46"/>
-      <c r="I130" s="77"/>
+      <c r="A130" s="43"/>
+      <c r="I130" s="43"/>
     </row>
     <row r="131" ht="13.5" customHeight="1">
-      <c r="A131" s="46"/>
-      <c r="I131" s="77"/>
+      <c r="A131" s="43"/>
+      <c r="I131" s="43"/>
     </row>
     <row r="132" ht="13.5" customHeight="1">
-      <c r="A132" s="46"/>
-      <c r="I132" s="77"/>
+      <c r="A132" s="43"/>
+      <c r="I132" s="43"/>
     </row>
     <row r="133" ht="13.5" customHeight="1">
-      <c r="A133" s="46"/>
-      <c r="I133" s="77"/>
+      <c r="A133" s="43"/>
+      <c r="I133" s="43"/>
     </row>
     <row r="134" ht="13.5" customHeight="1">
-      <c r="A134" s="46"/>
-      <c r="I134" s="77"/>
+      <c r="A134" s="43"/>
+      <c r="I134" s="43"/>
     </row>
     <row r="135" ht="13.5" customHeight="1">
-      <c r="A135" s="46"/>
-      <c r="I135" s="77"/>
+      <c r="A135" s="43"/>
+      <c r="I135" s="43"/>
     </row>
     <row r="136" ht="13.5" customHeight="1">
-      <c r="A136" s="46"/>
-      <c r="I136" s="77"/>
+      <c r="A136" s="43"/>
+      <c r="I136" s="43"/>
     </row>
     <row r="137" ht="13.5" customHeight="1">
-      <c r="A137" s="46"/>
-      <c r="I137" s="77"/>
+      <c r="A137" s="43"/>
+      <c r="I137" s="43"/>
     </row>
     <row r="138" ht="13.5" customHeight="1">
-      <c r="A138" s="46"/>
-      <c r="I138" s="77"/>
+      <c r="A138" s="43"/>
+      <c r="I138" s="43"/>
     </row>
     <row r="139" ht="13.5" customHeight="1">
-      <c r="A139" s="46"/>
-      <c r="I139" s="77"/>
+      <c r="A139" s="43"/>
+      <c r="I139" s="43"/>
     </row>
     <row r="140" ht="13.5" customHeight="1">
-      <c r="A140" s="46"/>
-      <c r="I140" s="77"/>
+      <c r="A140" s="43"/>
+      <c r="I140" s="43"/>
     </row>
     <row r="141" ht="13.5" customHeight="1">
-      <c r="A141" s="46"/>
-      <c r="I141" s="77"/>
+      <c r="A141" s="43"/>
+      <c r="I141" s="43"/>
     </row>
     <row r="142" ht="13.5" customHeight="1">
-      <c r="A142" s="46"/>
-      <c r="I142" s="77"/>
+      <c r="A142" s="43"/>
+      <c r="I142" s="43"/>
     </row>
     <row r="143" ht="13.5" customHeight="1">
-      <c r="A143" s="46"/>
-      <c r="I143" s="77"/>
+      <c r="A143" s="43"/>
+      <c r="I143" s="43"/>
     </row>
     <row r="144" ht="13.5" customHeight="1">
-      <c r="A144" s="46"/>
-      <c r="I144" s="77"/>
+      <c r="A144" s="43"/>
+      <c r="I144" s="43"/>
     </row>
     <row r="145" ht="13.5" customHeight="1">
-      <c r="A145" s="46"/>
-      <c r="I145" s="77"/>
+      <c r="A145" s="43"/>
+      <c r="I145" s="43"/>
     </row>
     <row r="146" ht="13.5" customHeight="1">
-      <c r="A146" s="46"/>
-      <c r="I146" s="77"/>
+      <c r="A146" s="43"/>
+      <c r="I146" s="43"/>
     </row>
     <row r="147" ht="13.5" customHeight="1">
-      <c r="A147" s="46"/>
-      <c r="I147" s="77"/>
+      <c r="A147" s="43"/>
+      <c r="I147" s="43"/>
     </row>
     <row r="148" ht="13.5" customHeight="1">
-      <c r="A148" s="46"/>
-      <c r="I148" s="77"/>
+      <c r="A148" s="43"/>
+      <c r="I148" s="43"/>
     </row>
     <row r="149" ht="13.5" customHeight="1">
-      <c r="A149" s="46"/>
-      <c r="I149" s="77"/>
+      <c r="A149" s="43"/>
+      <c r="I149" s="43"/>
     </row>
     <row r="150" ht="13.5" customHeight="1">
-      <c r="A150" s="46"/>
-      <c r="I150" s="77"/>
+      <c r="A150" s="43"/>
+      <c r="I150" s="43"/>
     </row>
     <row r="151" ht="13.5" customHeight="1">
-      <c r="A151" s="46"/>
-      <c r="I151" s="77"/>
+      <c r="A151" s="43"/>
+      <c r="I151" s="43"/>
     </row>
     <row r="152" ht="13.5" customHeight="1">
-      <c r="A152" s="46"/>
-      <c r="I152" s="77"/>
+      <c r="A152" s="43"/>
+      <c r="I152" s="43"/>
     </row>
     <row r="153" ht="13.5" customHeight="1">
-      <c r="A153" s="46"/>
-      <c r="I153" s="77"/>
+      <c r="A153" s="43"/>
+      <c r="I153" s="43"/>
     </row>
     <row r="154" ht="13.5" customHeight="1">
-      <c r="A154" s="46"/>
-      <c r="I154" s="77"/>
+      <c r="A154" s="43"/>
+      <c r="I154" s="43"/>
     </row>
     <row r="155" ht="13.5" customHeight="1">
-      <c r="A155" s="46"/>
-      <c r="I155" s="77"/>
+      <c r="A155" s="43"/>
+      <c r="I155" s="43"/>
     </row>
     <row r="156" ht="13.5" customHeight="1">
-      <c r="A156" s="46"/>
-      <c r="I156" s="77"/>
+      <c r="A156" s="43"/>
+      <c r="I156" s="43"/>
     </row>
     <row r="157" ht="13.5" customHeight="1">
-      <c r="A157" s="46"/>
-      <c r="I157" s="77"/>
+      <c r="A157" s="43"/>
+      <c r="I157" s="43"/>
     </row>
     <row r="158" ht="13.5" customHeight="1">
-      <c r="A158" s="46"/>
-      <c r="I158" s="77"/>
+      <c r="A158" s="43"/>
+      <c r="I158" s="43"/>
     </row>
     <row r="159" ht="13.5" customHeight="1">
-      <c r="A159" s="46"/>
-      <c r="I159" s="77"/>
+      <c r="A159" s="43"/>
+      <c r="I159" s="43"/>
     </row>
     <row r="160" ht="13.5" customHeight="1">
-      <c r="A160" s="46"/>
-      <c r="I160" s="77"/>
+      <c r="A160" s="43"/>
+      <c r="I160" s="43"/>
     </row>
     <row r="161" ht="13.5" customHeight="1">
-      <c r="A161" s="46"/>
-      <c r="I161" s="77"/>
+      <c r="A161" s="43"/>
+      <c r="I161" s="43"/>
     </row>
     <row r="162" ht="13.5" customHeight="1">
-      <c r="A162" s="46"/>
-      <c r="I162" s="77"/>
+      <c r="A162" s="43"/>
+      <c r="I162" s="43"/>
     </row>
     <row r="163" ht="13.5" customHeight="1">
-      <c r="A163" s="46"/>
-      <c r="I163" s="77"/>
+      <c r="A163" s="43"/>
+      <c r="I163" s="43"/>
     </row>
     <row r="164" ht="13.5" customHeight="1">
-      <c r="A164" s="46"/>
-      <c r="I164" s="77"/>
+      <c r="A164" s="43"/>
+      <c r="I164" s="43"/>
     </row>
     <row r="165" ht="13.5" customHeight="1">
-      <c r="A165" s="46"/>
-      <c r="I165" s="77"/>
+      <c r="A165" s="43"/>
+      <c r="I165" s="43"/>
     </row>
     <row r="166" ht="13.5" customHeight="1">
-      <c r="A166" s="46"/>
-      <c r="I166" s="77"/>
+      <c r="A166" s="43"/>
+      <c r="I166" s="43"/>
     </row>
     <row r="167" ht="13.5" customHeight="1">
-      <c r="A167" s="46"/>
-      <c r="I167" s="77"/>
+      <c r="A167" s="43"/>
+      <c r="I167" s="43"/>
     </row>
     <row r="168" ht="13.5" customHeight="1">
-      <c r="A168" s="46"/>
-      <c r="I168" s="77"/>
+      <c r="A168" s="43"/>
+      <c r="I168" s="43"/>
     </row>
     <row r="169" ht="13.5" customHeight="1">
-      <c r="A169" s="46"/>
-      <c r="I169" s="77"/>
+      <c r="A169" s="43"/>
+      <c r="I169" s="43"/>
     </row>
     <row r="170" ht="13.5" customHeight="1">
-      <c r="A170" s="46"/>
-      <c r="I170" s="77"/>
+      <c r="A170" s="43"/>
+      <c r="I170" s="43"/>
     </row>
     <row r="171" ht="13.5" customHeight="1">
-      <c r="A171" s="46"/>
-      <c r="I171" s="77"/>
+      <c r="A171" s="43"/>
+      <c r="I171" s="43"/>
     </row>
     <row r="172" ht="13.5" customHeight="1">
-      <c r="A172" s="46"/>
-      <c r="I172" s="77"/>
+      <c r="A172" s="43"/>
+      <c r="I172" s="43"/>
     </row>
     <row r="173" ht="13.5" customHeight="1">
-      <c r="A173" s="46"/>
-      <c r="I173" s="77"/>
+      <c r="A173" s="43"/>
+      <c r="I173" s="43"/>
     </row>
     <row r="174" ht="13.5" customHeight="1">
-      <c r="A174" s="46"/>
-      <c r="I174" s="77"/>
+      <c r="A174" s="43"/>
+      <c r="I174" s="43"/>
     </row>
     <row r="175" ht="13.5" customHeight="1">
-      <c r="A175" s="46"/>
-      <c r="I175" s="77"/>
+      <c r="A175" s="43"/>
+      <c r="I175" s="43"/>
     </row>
     <row r="176" ht="13.5" customHeight="1">
-      <c r="A176" s="46"/>
-      <c r="I176" s="77"/>
+      <c r="A176" s="43"/>
+      <c r="I176" s="43"/>
     </row>
     <row r="177" ht="13.5" customHeight="1">
-      <c r="A177" s="46"/>
-      <c r="I177" s="77"/>
+      <c r="A177" s="43"/>
+      <c r="I177" s="43"/>
     </row>
     <row r="178" ht="13.5" customHeight="1">
-      <c r="A178" s="46"/>
-      <c r="I178" s="77"/>
+      <c r="A178" s="43"/>
+      <c r="I178" s="43"/>
     </row>
     <row r="179" ht="13.5" customHeight="1">
-      <c r="A179" s="46"/>
-      <c r="I179" s="77"/>
+      <c r="A179" s="43"/>
+      <c r="I179" s="43"/>
     </row>
     <row r="180" ht="13.5" customHeight="1">
-      <c r="A180" s="46"/>
-      <c r="I180" s="77"/>
+      <c r="A180" s="43"/>
+      <c r="I180" s="43"/>
     </row>
     <row r="181" ht="13.5" customHeight="1">
-      <c r="A181" s="46"/>
-      <c r="I181" s="77"/>
+      <c r="A181" s="43"/>
+      <c r="I181" s="43"/>
     </row>
     <row r="182" ht="13.5" customHeight="1">
-      <c r="A182" s="46"/>
-      <c r="I182" s="77"/>
+      <c r="A182" s="43"/>
+      <c r="I182" s="43"/>
     </row>
     <row r="183" ht="13.5" customHeight="1">
-      <c r="A183" s="46"/>
-      <c r="I183" s="77"/>
+      <c r="A183" s="43"/>
+      <c r="I183" s="43"/>
     </row>
     <row r="184" ht="13.5" customHeight="1">
-      <c r="A184" s="46"/>
-      <c r="I184" s="77"/>
+      <c r="A184" s="43"/>
+      <c r="I184" s="43"/>
     </row>
     <row r="185" ht="13.5" customHeight="1">
-      <c r="A185" s="46"/>
-      <c r="I185" s="77"/>
+      <c r="A185" s="43"/>
+      <c r="I185" s="43"/>
     </row>
     <row r="186" ht="13.5" customHeight="1">
-      <c r="A186" s="46"/>
-      <c r="I186" s="77"/>
+      <c r="A186" s="43"/>
+      <c r="I186" s="43"/>
     </row>
     <row r="187" ht="13.5" customHeight="1">
-      <c r="A187" s="46"/>
-      <c r="I187" s="77"/>
+      <c r="A187" s="43"/>
+      <c r="I187" s="43"/>
     </row>
     <row r="188" ht="13.5" customHeight="1">
-      <c r="A188" s="46"/>
-      <c r="I188" s="77"/>
+      <c r="A188" s="43"/>
+      <c r="I188" s="43"/>
     </row>
     <row r="189" ht="13.5" customHeight="1">
-      <c r="A189" s="46"/>
-      <c r="I189" s="77"/>
+      <c r="A189" s="43"/>
+      <c r="I189" s="43"/>
     </row>
     <row r="190" ht="13.5" customHeight="1">
-      <c r="A190" s="46"/>
-      <c r="I190" s="77"/>
+      <c r="A190" s="43"/>
+      <c r="I190" s="43"/>
     </row>
     <row r="191" ht="13.5" customHeight="1">
-      <c r="A191" s="46"/>
-      <c r="I191" s="77"/>
+      <c r="A191" s="43"/>
+      <c r="I191" s="43"/>
     </row>
     <row r="192" ht="13.5" customHeight="1">
-      <c r="A192" s="46"/>
-      <c r="I192" s="77"/>
+      <c r="A192" s="43"/>
+      <c r="I192" s="43"/>
     </row>
     <row r="193" ht="13.5" customHeight="1">
-      <c r="A193" s="46"/>
-      <c r="I193" s="77"/>
+      <c r="A193" s="43"/>
+      <c r="I193" s="43"/>
     </row>
     <row r="194" ht="13.5" customHeight="1">
-      <c r="A194" s="46"/>
-      <c r="I194" s="77"/>
+      <c r="A194" s="43"/>
+      <c r="I194" s="43"/>
     </row>
     <row r="195" ht="13.5" customHeight="1">
-      <c r="A195" s="46"/>
-      <c r="I195" s="77"/>
+      <c r="A195" s="43"/>
+      <c r="I195" s="43"/>
     </row>
     <row r="196" ht="13.5" customHeight="1">
-      <c r="A196" s="46"/>
-      <c r="I196" s="77"/>
+      <c r="A196" s="43"/>
+      <c r="I196" s="43"/>
     </row>
     <row r="197" ht="13.5" customHeight="1">
-      <c r="A197" s="46"/>
-      <c r="I197" s="77"/>
+      <c r="A197" s="43"/>
+      <c r="I197" s="43"/>
     </row>
     <row r="198" ht="13.5" customHeight="1">
-      <c r="A198" s="46"/>
-      <c r="I198" s="77"/>
+      <c r="A198" s="43"/>
+      <c r="I198" s="43"/>
     </row>
     <row r="199" ht="13.5" customHeight="1">
-      <c r="A199" s="46"/>
-      <c r="I199" s="77"/>
+      <c r="A199" s="43"/>
+      <c r="I199" s="43"/>
     </row>
     <row r="200" ht="13.5" customHeight="1">
-      <c r="A200" s="46"/>
-      <c r="I200" s="77"/>
+      <c r="A200" s="43"/>
+      <c r="I200" s="43"/>
     </row>
     <row r="201" ht="13.5" customHeight="1">
-      <c r="A201" s="46"/>
-      <c r="I201" s="77"/>
+      <c r="A201" s="43"/>
+      <c r="I201" s="43"/>
     </row>
     <row r="202" ht="13.5" customHeight="1">
-      <c r="A202" s="46"/>
-      <c r="I202" s="77"/>
+      <c r="A202" s="43"/>
+      <c r="I202" s="43"/>
     </row>
     <row r="203" ht="13.5" customHeight="1">
-      <c r="A203" s="46"/>
-      <c r="I203" s="77"/>
+      <c r="A203" s="43"/>
+      <c r="I203" s="43"/>
     </row>
     <row r="204" ht="13.5" customHeight="1">
-      <c r="A204" s="46"/>
-      <c r="I204" s="77"/>
+      <c r="A204" s="43"/>
+      <c r="I204" s="43"/>
     </row>
     <row r="205" ht="13.5" customHeight="1">
-      <c r="A205" s="46"/>
-      <c r="I205" s="77"/>
+      <c r="A205" s="43"/>
+      <c r="I205" s="43"/>
     </row>
     <row r="206" ht="13.5" customHeight="1">
-      <c r="A206" s="46"/>
-      <c r="I206" s="77"/>
+      <c r="A206" s="43"/>
+      <c r="I206" s="43"/>
     </row>
     <row r="207" ht="13.5" customHeight="1">
-      <c r="A207" s="46"/>
-      <c r="I207" s="77"/>
+      <c r="A207" s="43"/>
+      <c r="I207" s="43"/>
     </row>
     <row r="208" ht="13.5" customHeight="1">
-      <c r="A208" s="46"/>
-      <c r="I208" s="77"/>
+      <c r="A208" s="43"/>
+      <c r="I208" s="43"/>
     </row>
     <row r="209" ht="13.5" customHeight="1">
-      <c r="A209" s="46"/>
-      <c r="I209" s="77"/>
+      <c r="A209" s="43"/>
+      <c r="I209" s="43"/>
     </row>
     <row r="210" ht="13.5" customHeight="1">
-      <c r="A210" s="46"/>
-      <c r="I210" s="77"/>
+      <c r="A210" s="43"/>
+      <c r="I210" s="43"/>
     </row>
     <row r="211" ht="13.5" customHeight="1">
-      <c r="A211" s="46"/>
-      <c r="I211" s="77"/>
+      <c r="A211" s="43"/>
+      <c r="I211" s="43"/>
     </row>
     <row r="212" ht="13.5" customHeight="1">
-      <c r="A212" s="46"/>
-      <c r="I212" s="77"/>
+      <c r="A212" s="43"/>
+      <c r="I212" s="43"/>
     </row>
     <row r="213" ht="13.5" customHeight="1">
-      <c r="A213" s="46"/>
-      <c r="I213" s="77"/>
+      <c r="A213" s="43"/>
+      <c r="I213" s="43"/>
     </row>
     <row r="214" ht="13.5" customHeight="1">
-      <c r="A214" s="46"/>
-      <c r="I214" s="77"/>
+      <c r="A214" s="43"/>
+      <c r="I214" s="43"/>
     </row>
     <row r="215" ht="13.5" customHeight="1">
-      <c r="A215" s="46"/>
-      <c r="I215" s="77"/>
+      <c r="A215" s="43"/>
+      <c r="I215" s="43"/>
     </row>
     <row r="216" ht="13.5" customHeight="1">
-      <c r="A216" s="46"/>
-      <c r="I216" s="77"/>
+      <c r="A216" s="43"/>
+      <c r="I216" s="43"/>
     </row>
     <row r="217" ht="13.5" customHeight="1">
-      <c r="A217" s="46"/>
-      <c r="I217" s="77"/>
+      <c r="A217" s="43"/>
+      <c r="I217" s="43"/>
     </row>
     <row r="218" ht="13.5" customHeight="1">
-      <c r="A218" s="46"/>
-      <c r="I218" s="77"/>
+      <c r="A218" s="43"/>
     </row>
     <row r="219" ht="13.5" customHeight="1">
-      <c r="A219" s="46"/>
-      <c r="I219" s="77"/>
+      <c r="A219" s="43"/>
     </row>
     <row r="220" ht="13.5" customHeight="1">
-      <c r="A220" s="46"/>
-      <c r="I220" s="77"/>
+      <c r="A220" s="43"/>
     </row>
     <row r="221" ht="13.5" customHeight="1">
-      <c r="A221" s="46"/>
-      <c r="I221" s="77"/>
+      <c r="A221" s="43"/>
     </row>
     <row r="222" ht="13.5" customHeight="1">
-      <c r="A222" s="46"/>
-      <c r="I222" s="77"/>
+      <c r="A222" s="43"/>
     </row>
     <row r="223" ht="13.5" customHeight="1">
-      <c r="A223" s="46"/>
-      <c r="I223" s="77"/>
+      <c r="A223" s="43"/>
     </row>
     <row r="224" ht="13.5" customHeight="1">
-      <c r="A224" s="46"/>
-      <c r="I224" s="77"/>
+      <c r="A224" s="43"/>
     </row>
     <row r="225" ht="13.5" customHeight="1">
-      <c r="A225" s="46"/>
-      <c r="I225" s="77"/>
+      <c r="A225" s="43"/>
     </row>
     <row r="226" ht="13.5" customHeight="1">
-      <c r="A226" s="46"/>
-      <c r="I226" s="77"/>
+      <c r="A226" s="43"/>
     </row>
     <row r="227" ht="13.5" customHeight="1">
-      <c r="A227" s="46"/>
-      <c r="I227" s="77"/>
+      <c r="A227" s="43"/>
     </row>
     <row r="228" ht="13.5" customHeight="1">
-      <c r="A228" s="46"/>
-      <c r="I228" s="77"/>
+      <c r="A228" s="43"/>
     </row>
     <row r="229" ht="13.5" customHeight="1">
-      <c r="A229" s="46"/>
-      <c r="I229" s="77"/>
+      <c r="A229" s="43"/>
     </row>
     <row r="230" ht="13.5" customHeight="1">
-      <c r="A230" s="46"/>
-      <c r="I230" s="77"/>
+      <c r="A230" s="43"/>
     </row>
     <row r="231" ht="13.5" customHeight="1">
-      <c r="A231" s="46"/>
-      <c r="I231" s="77"/>
+      <c r="A231" s="43"/>
     </row>
     <row r="232" ht="13.5" customHeight="1">
-      <c r="A232" s="46"/>
-      <c r="I232" s="77"/>
+      <c r="A232" s="43"/>
     </row>
     <row r="233" ht="13.5" customHeight="1">
-      <c r="A233" s="46"/>
-      <c r="I233" s="77"/>
+      <c r="A233" s="43"/>
     </row>
     <row r="234" ht="13.5" customHeight="1">
-      <c r="A234" s="46"/>
-      <c r="I234" s="77"/>
+      <c r="A234" s="43"/>
     </row>
     <row r="235" ht="13.5" customHeight="1">
-      <c r="A235" s="46"/>
-      <c r="I235" s="77"/>
+      <c r="A235" s="43"/>
     </row>
     <row r="236" ht="13.5" customHeight="1">
-      <c r="A236" s="46"/>
-      <c r="I236" s="77"/>
+      <c r="A236" s="43"/>
     </row>
     <row r="237" ht="13.5" customHeight="1">
-      <c r="A237" s="46"/>
-      <c r="I237" s="77"/>
+      <c r="A237" s="43"/>
     </row>
     <row r="238" ht="13.5" customHeight="1">
-      <c r="A238" s="46"/>
-      <c r="I238" s="77"/>
+      <c r="A238" s="43"/>
     </row>
     <row r="239" ht="13.5" customHeight="1">
-      <c r="A239" s="46"/>
-      <c r="I239" s="77"/>
+      <c r="A239" s="43"/>
     </row>
     <row r="240" ht="13.5" customHeight="1">
-      <c r="A240" s="46"/>
-      <c r="I240" s="77"/>
+      <c r="A240" s="43"/>
     </row>
     <row r="241" ht="13.5" customHeight="1">
-      <c r="A241" s="46"/>
-      <c r="I241" s="77"/>
+      <c r="A241" s="43"/>
     </row>
     <row r="242" ht="13.5" customHeight="1">
-      <c r="A242" s="46"/>
-      <c r="I242" s="77"/>
+      <c r="A242" s="43"/>
     </row>
     <row r="243" ht="13.5" customHeight="1">
-      <c r="A243" s="46"/>
-      <c r="I243" s="77"/>
+      <c r="A243" s="43"/>
     </row>
     <row r="244" ht="13.5" customHeight="1">
-      <c r="A244" s="46"/>
-      <c r="I244" s="77"/>
+      <c r="A244" s="43"/>
     </row>
     <row r="245" ht="13.5" customHeight="1">
-      <c r="A245" s="46"/>
-      <c r="I245" s="77"/>
+      <c r="A245" s="43"/>
     </row>
     <row r="246" ht="13.5" customHeight="1">
-      <c r="A246" s="46"/>
-      <c r="I246" s="77"/>
+      <c r="A246" s="43"/>
     </row>
     <row r="247" ht="13.5" customHeight="1">
-      <c r="A247" s="46"/>
-      <c r="I247" s="77"/>
+      <c r="A247" s="43"/>
     </row>
     <row r="248" ht="13.5" customHeight="1">
-      <c r="A248" s="46"/>
-      <c r="I248" s="77"/>
+      <c r="A248" s="43"/>
     </row>
     <row r="249" ht="13.5" customHeight="1">
-      <c r="A249" s="46"/>
-      <c r="I249" s="77"/>
+      <c r="A249" s="43"/>
     </row>
     <row r="250" ht="13.5" customHeight="1">
-      <c r="A250" s="46"/>
-      <c r="I250" s="77"/>
+      <c r="A250" s="43"/>
     </row>
     <row r="251" ht="13.5" customHeight="1">
-      <c r="A251" s="46"/>
-      <c r="I251" s="77"/>
+      <c r="A251" s="43"/>
     </row>
     <row r="252" ht="13.5" customHeight="1">
-      <c r="A252" s="46"/>
-      <c r="I252" s="77"/>
+      <c r="A252" s="43"/>
     </row>
     <row r="253" ht="13.5" customHeight="1">
-      <c r="A253" s="46"/>
-      <c r="I253" s="77"/>
+      <c r="A253" s="43"/>
     </row>
     <row r="254" ht="13.5" customHeight="1">
-      <c r="A254" s="46"/>
-      <c r="I254" s="77"/>
+      <c r="A254" s="43"/>
     </row>
     <row r="255" ht="13.5" customHeight="1">
-      <c r="A255" s="46"/>
-      <c r="I255" s="77"/>
+      <c r="A255" s="43"/>
     </row>
     <row r="256" ht="13.5" customHeight="1">
-      <c r="A256" s="46"/>
-      <c r="I256" s="77"/>
+      <c r="A256" s="43"/>
     </row>
     <row r="257" ht="13.5" customHeight="1">
-      <c r="A257" s="46"/>
-      <c r="I257" s="77"/>
+      <c r="A257" s="43"/>
     </row>
     <row r="258" ht="13.5" customHeight="1">
-      <c r="A258" s="46"/>
-      <c r="I258" s="77"/>
+      <c r="A258" s="43"/>
     </row>
     <row r="259" ht="13.5" customHeight="1">
-      <c r="A259" s="46"/>
-      <c r="I259" s="77"/>
+      <c r="A259" s="43"/>
     </row>
     <row r="260" ht="13.5" customHeight="1">
-      <c r="A260" s="46"/>
-      <c r="I260" s="77"/>
+      <c r="A260" s="43"/>
     </row>
     <row r="261" ht="13.5" customHeight="1">
-      <c r="A261" s="46"/>
-      <c r="I261" s="77"/>
+      <c r="A261" s="43"/>
     </row>
     <row r="262" ht="13.5" customHeight="1">
-      <c r="A262" s="46"/>
-      <c r="I262" s="77"/>
+      <c r="A262" s="43"/>
     </row>
     <row r="263" ht="13.5" customHeight="1">
-      <c r="A263" s="46"/>
-      <c r="I263" s="77"/>
+      <c r="A263" s="43"/>
     </row>
     <row r="264" ht="13.5" customHeight="1">
-      <c r="A264" s="46"/>
-      <c r="I264" s="77"/>
+      <c r="A264" s="43"/>
     </row>
     <row r="265" ht="13.5" customHeight="1">
-      <c r="A265" s="46"/>
-      <c r="I265" s="77"/>
+      <c r="A265" s="43"/>
     </row>
     <row r="266" ht="13.5" customHeight="1">
-      <c r="A266" s="46"/>
-      <c r="I266" s="77"/>
+      <c r="A266" s="43"/>
     </row>
     <row r="267" ht="13.5" customHeight="1">
-      <c r="A267" s="46"/>
-      <c r="I267" s="77"/>
+      <c r="A267" s="43"/>
     </row>
     <row r="268" ht="13.5" customHeight="1">
-      <c r="A268" s="46"/>
-      <c r="I268" s="77"/>
+      <c r="A268" s="43"/>
     </row>
     <row r="269" ht="13.5" customHeight="1">
-      <c r="A269" s="46"/>
-      <c r="I269" s="77"/>
+      <c r="A269" s="43"/>
     </row>
     <row r="270" ht="13.5" customHeight="1">
-      <c r="A270" s="46"/>
-      <c r="I270" s="77"/>
+      <c r="A270" s="43"/>
     </row>
     <row r="271" ht="13.5" customHeight="1">
-      <c r="A271" s="46"/>
+      <c r="A271" s="43"/>
     </row>
     <row r="272" ht="13.5" customHeight="1"/>
     <row r="273" ht="13.5" customHeight="1"/>
@@ -2906,7 +2813,7 @@
     <row r="729" ht="13.5" customHeight="1"/>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{B11FEEE2-625F-4AAF-8B49-E70FE5F66624}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{4642DB06-625C-40F7-B187-56563CB26E82}" filter="1" showAutoFilter="1">
       <autoFilter ref="$I$1:$I$563"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
@@ -2914,7 +2821,7 @@
         </ext>
       </extLst>
     </customSheetView>
-    <customSheetView guid="{E030274F-D8A4-4B1C-84F1-2CAF425A2CE5}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{8DF02645-97DB-4BA1-8860-6E858A7D8324}" filter="1" showAutoFilter="1">
       <autoFilter ref="$I$1:$I$563"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">

--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -17,6 +17,7 @@
     <definedName name="RATES_EXPEDITION">#REF!</definedName>
     <definedName name="RATES_PRODUCTION">#REF!</definedName>
     <definedName name="RATES_CREATIVE">#REF!</definedName>
+    <definedName name="date">EXPORT_TMP!$C$21</definedName>
     <definedName name="Smen">#REF!</definedName>
     <definedName name="Actors1">#REF!</definedName>
     <definedName name="markup">#REF!</definedName>
@@ -24,7 +25,6 @@
     <definedName name="RATES_OVERTIME">#REF!</definedName>
     <definedName name="TAX_FOR_CLENT">#REF!</definedName>
     <definedName name="ACTUAL">#REF!</definedName>
-    <definedName name="date">EXPORT_TMP!$C$21:$D$21</definedName>
     <definedName name="RATES_EDITING">#REF!</definedName>
     <definedName name="RATES_PROD_PEOPLE">#REF!</definedName>
     <definedName name="TAX_FOR_CLENT_TYPE">#REF!</definedName>
@@ -44,8 +44,8 @@
     <definedName name="Templates">#REF!</definedName>
     <definedName name="hronSEC">#REF!</definedName>
     <definedName localSheetId="0" name="SMETA_TITLE">EXPORT_TMP!$B$7</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_8DF02645_97DB_4BA1_8860_6E858A7D8324_.wvu.FilterData">EXPORT_TMP!$I$1:$I$563</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_4642DB06_625C_40F7_B187_56563CB26E82_.wvu.FilterData">EXPORT_TMP!$I$1:$I$563</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_3C06C552_476B_4A1C_9EC5_66F876A9579D_.wvu.FilterData">EXPORT_TMP!$I$1:$I$563</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_FA1D313F_DA59_43BE_9F29_26CE50AE4C0B_.wvu.FilterData">EXPORT_TMP!$I$1:$I$563</definedName>
     <definedName name="CLIENT_PRICE">LAMBDA(себестоимость, вашмаркап, налог, округление, IFERROR(ROUNDUP(себестоимость*(1+вашмаркап/100)/(1-1*налог),округление),0))</definedName>
     <definedName name="CONDUCT_CALC">LAMBDA(стоимость, количество, налог, IFERROR(PRODUCT(количество, стоимость) / TAX_CONVERTER(налог), 0))</definedName>
     <definedName name="MARKET_FEE">LAMBDA(процент, сумма_до_налога, MIN(сумма_до_налога, 2000000) * процент + MAX(0, сумма_до_налога - 2000000) * (процент / 2))</definedName>
@@ -53,12 +53,12 @@
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{4642DB06-625C-40F7-B187-56563CB26E82}" name="nozero"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{8DF02645-97DB-4BA1-8860-6E858A7D8324}" name="WithZeros"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{FA1D313F-DA59-43BE-9F29-26CE50AE4C0B}" name="nozero"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{3C06C552-476B-4A1C-9EC5-66F876A9579D}" name="WithZeros"/>
   </customWorkbookViews>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="mkShwr18k5ApuBk9XfsX27uxgyu4LFyGdc20tGiYOFs="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Y+7JQsi+L3rOEdCuxO/yb7M33SpWrTNRVfoUkOQpFkE="/>
     </ext>
   </extLst>
 </workbook>
@@ -2813,7 +2813,7 @@
     <row r="729" ht="13.5" customHeight="1"/>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{4642DB06-625C-40F7-B187-56563CB26E82}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{FA1D313F-DA59-43BE-9F29-26CE50AE4C0B}" filter="1" showAutoFilter="1">
       <autoFilter ref="$I$1:$I$563"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
@@ -2821,7 +2821,7 @@
         </ext>
       </extLst>
     </customSheetView>
-    <customSheetView guid="{8DF02645-97DB-4BA1-8860-6E858A7D8324}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{3C06C552-476B-4A1C-9EC5-66F876A9579D}" filter="1" showAutoFilter="1">
       <autoFilter ref="$I$1:$I$563"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
@@ -2842,12 +2842,12 @@
     <mergeCell ref="C27:H27"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="D19:F19"/>
-    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E21:H21"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C23:H23"/>
     <mergeCell ref="C24:H24"/>
     <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C21:D21"/>
   </mergeCells>
   <conditionalFormatting sqref="G9 G11 G19">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
